--- a/baby/posts/20260807-noti-checklist/files/출산준비물_체크리스트_보아르아가노트.xlsx
+++ b/baby/posts/20260807-noti-checklist/files/출산준비물_체크리스트_보아르아가노트.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="읽어주세요" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'출산준비물 체크리스트'!$A$3:$G$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'출산준비물 체크리스트'!$A$3:$G$146</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -543,7 +543,7 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>출산 준비물 체크리스트  ·  총 100개</t>
+          <t>출산 준비물 체크리스트  ·  총 143개</t>
         </is>
       </c>
     </row>
@@ -678,12 +678,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>산모패드 (대·중·소)</t>
+          <t>산모패드 (대)</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>1세트</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>병원에서 주는 경우 많음 — 미리 확인하고 사세요</t>
+          <t>대 사이즈 하나면 충분합니다</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>일회용 팬티</t>
+          <t>맘스안심팬티</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>5~7</t>
+          <t>2팩</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>세면도구</t>
+          <t>손수건</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>1세트</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -836,7 +836,11 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr"/>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>젖몸살 왔을 때 아이스팩에 둘러서 쓰면 좋아요. 그 외에도 두루두루 씁니다</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -851,12 +855,12 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>텀블러 · 빨대컵</t>
+          <t>세면도구</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1세트</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
@@ -869,11 +873,7 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
-        <is>
-          <t>누워서 마셔야 해서 빨대가 편합니다</t>
-        </is>
-      </c>
+      <c r="G11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>손목보호대</t>
+          <t>텀블러 · 빨대컵</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>손목 통증은 거의 모두 겪습니다</t>
+          <t>누워서 마셔야 해서 빨대가 편합니다</t>
         </is>
       </c>
     </row>
@@ -925,17 +925,17 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>복대</t>
+          <t>텀블러 세척도구 (수세미·세제)</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>1세트</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>제왕절개면 필수</t>
+          <t>텀블러만 챙기고 씻을 걸 안 챙기면 곤란해집니다</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>슬리퍼</t>
+          <t>손목보호대</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -980,7 +980,11 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr"/>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>손목 통증은 거의 모두 겪습니다</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -995,7 +999,7 @@
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>겉옷 (가디건)</t>
+          <t>복대</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -1003,9 +1007,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>필수</t>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
@@ -1013,7 +1017,11 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr"/>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>제왕절개면 필수</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1028,7 +1036,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>충전기 (긴 케이블)</t>
+          <t>슬리퍼</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1046,11 +1054,7 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>침대에서 콘센트가 멉니다</t>
-        </is>
-      </c>
+      <c r="G16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -1065,7 +1069,7 @@
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>회음부 방석</t>
+          <t>겉옷 (가디건)</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -1073,9 +1077,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>보통</t>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
@@ -1083,11 +1087,7 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
-        <is>
-          <t>자연분만 시</t>
-        </is>
-      </c>
+      <c r="G17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>물티슈</t>
+          <t>충전기 (긴 케이블)</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1120,7 +1120,11 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr"/>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>침대에서 콘센트가 멉니다</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -1135,27 +1139,27 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>맘스안심팬티</t>
+          <t>회음부 방석</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>굳이</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>34주</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>후회템으로 자주 꼽힙니다</t>
+          <t>자연분만 시</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1171,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>병원 · 아기</t>
+          <t>병원 · 산모</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>배냇저고리</t>
+          <t>물티슈</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1190,11 +1194,7 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>퇴원 때 입힐 것</t>
-        </is>
-      </c>
+      <c r="G20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -1204,17 +1204,17 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>병원 · 아기</t>
+          <t>병원 · 산모</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>속싸개</t>
+          <t>가슴 열감 완화팩</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>1~2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
@@ -1227,7 +1227,11 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G21" s="11" t="inlineStr"/>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>젖몸살은 거의 모두 겪습니다. 손수건에 둘러서 쓰세요</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -1237,12 +1241,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>병원 · 아기</t>
+          <t>병원 · 산모</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>겉싸개</t>
+          <t>산모 치약</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1250,9 +1254,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>필수</t>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1262,7 +1266,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>계절 맞춰서</t>
+          <t>시린 이가 생기는 경우가 많습니다</t>
         </is>
       </c>
     </row>
@@ -1274,17 +1278,17 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>병원 · 아기</t>
+          <t>병원 · 산모</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>손싸개 · 아기모자</t>
+          <t>압박스타킹</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>1세트</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -1297,7 +1301,11 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G23" s="11" t="inlineStr"/>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>부기 완화용</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -1312,12 +1320,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>가제손수건</t>
+          <t>배냇저고리</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -1330,7 +1338,11 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr"/>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>퇴원 때 입힐 것</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -1345,12 +1357,12 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>신생아 카시트</t>
+          <t>아기 바지</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1~2</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
@@ -1360,12 +1372,12 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>32주</t>
+          <t>34주</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>퇴원 시 반드시 필요. 중고 절대 비추</t>
+          <t>집에 갈 때 카시트를 태워야 하는데, 바지가 없으면 맨다리가 됩니다</t>
         </is>
       </c>
     </row>
@@ -1377,17 +1389,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>조리원</t>
+          <t>병원 · 아기</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>편한 옷 (수유 가능)</t>
+          <t>속싸개</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3~4</t>
+          <t>1~2</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -1397,14 +1409,10 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>36주</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>앞트임 필수</t>
-        </is>
-      </c>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -1414,17 +1422,17 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>조리원</t>
+          <t>병원 · 아기</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>개인 세면도구</t>
+          <t>겉싸개</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>1세트</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E27" s="10" t="inlineStr">
@@ -1434,10 +1442,14 @@
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>36주</t>
-        </is>
-      </c>
-      <c r="G27" s="11" t="inlineStr"/>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>계절 맞춰서</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -1447,22 +1459,22 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>조리원</t>
+          <t>병원 · 아기</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>수유쿠션</t>
+          <t>손싸개 · 아기모자</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>필수</t>
+          <t>1세트</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -1480,34 +1492,30 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>조리원</t>
+          <t>병원 · 아기</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>유축기</t>
+          <t>가제손수건</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>36주</t>
-        </is>
-      </c>
-      <c r="G29" s="11" t="inlineStr">
-        <is>
-          <t>보건소 무료 대여 가능. 개인부품만 구매</t>
-        </is>
-      </c>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -1517,12 +1525,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>조리원</t>
+          <t>병원 · 아기</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>젖병 세정제</t>
+          <t>아기 유산균</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1537,10 +1545,14 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>34주</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr"/>
+          <t>36주</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>조리원에 맡기면 하루 한 번 먹여줍니다. 요즘은 비타민D가 포함된 제품(바이오가이아 이지드롭 등)을 많이 씁니다</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
@@ -1550,12 +1562,12 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>조리원</t>
+          <t>병원 · 아기</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>튼살크림</t>
+          <t>신생아 카시트</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
@@ -1563,17 +1575,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>보통</t>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G31" s="11" t="inlineStr"/>
+          <t>32주</t>
+        </is>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>퇴원 시 반드시 필요. 중고 절대 비추</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -1588,27 +1604,27 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>노트북 · 태블릿</t>
+          <t>편한 옷 (수유 가능)</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>3~4</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>36주</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>생각보다 시간이 많습니다</t>
+          <t>앞트임 필수</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1641,12 @@
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>산모용 슬리퍼</t>
+          <t>개인 세면도구</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1세트</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
@@ -1658,25 +1674,29 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>간식 · 보리차</t>
+          <t>콘센트 (멀티탭)</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="inlineStr"/>
+          <t>36주</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>침대 주변 콘센트가 부족합니다</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -1686,32 +1706,32 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>집 · 수유</t>
+          <t>조리원</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>젖병 (신생아 소용량)</t>
+          <t>수유쿠션</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>3~5</t>
-        </is>
-      </c>
-      <c r="E35" s="10" t="inlineStr">
-        <is>
-          <t>필수</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>굳이</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>34주</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
-          <t>처음부터 많이 사지 말고 아기 반응 보고 추가</t>
+          <t>요즘 조리원엔 대부분 비치돼 있습니다. 미리 확인해보세요</t>
         </is>
       </c>
     </row>
@@ -1723,17 +1743,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>집 · 수유</t>
+          <t>조리원</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>젖병 (중용량)</t>
+          <t>유축기</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>3~5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -1743,12 +1763,12 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>출산 후</t>
+          <t>36주</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>2~3개월부터 필요</t>
+          <t>보건소 무료 대여 가능. 개인부품만 구매</t>
         </is>
       </c>
     </row>
@@ -1760,17 +1780,17 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>집 · 수유</t>
+          <t>조리원</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>젖꼭지 여분</t>
+          <t>젖병 세정제</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>3~5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
@@ -1783,11 +1803,7 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G37" s="11" t="inlineStr">
-        <is>
-          <t>단계별로 교체해야 합니다</t>
-        </is>
-      </c>
+      <c r="G37" s="11" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -1797,27 +1813,27 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>집 · 수유</t>
+          <t>조리원</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>젖병솔 · 젖꼭지솔</t>
+          <t>튼살크림</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1세트</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>필수</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>34주</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr"/>
@@ -1830,12 +1846,12 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>집 · 수유</t>
+          <t>조리원</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>젖병 세정제</t>
+          <t>노트북 · 태블릿</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -1843,17 +1859,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E39" s="10" t="inlineStr">
-        <is>
-          <t>필수</t>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>34주</t>
-        </is>
-      </c>
-      <c r="G39" s="11" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>생각보다 시간이 많습니다</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -1863,12 +1883,12 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>집 · 수유</t>
+          <t>조리원</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>젖병소독기</t>
+          <t>산모용 슬리퍼</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1876,21 +1896,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>보통</t>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>34주</t>
-        </is>
-      </c>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>열탕소독으로 대체 가능하지만 손이 많이 갑니다</t>
-        </is>
-      </c>
+          <t>36주</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -1900,17 +1916,17 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>집 · 수유</t>
+          <t>조리원</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>젖병 건조대</t>
+          <t>간식 · 보리차</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -1920,7 +1936,7 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>34주</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr"/>
@@ -1938,12 +1954,12 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>분유</t>
+          <t>젖병 (신생아 소용량)</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1~2</t>
+          <t>3~5</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -1953,12 +1969,12 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>36주</t>
+          <t>34주</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>샘플 먼저 받아보고 결정</t>
+          <t>처음부터 많이 사지 말고 아기 반응 보고 추가</t>
         </is>
       </c>
     </row>
@@ -1975,12 +1991,12 @@
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>분유포트 (보온)</t>
+          <t>젖병 (중용량)</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3~5</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -1990,12 +2006,12 @@
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>34주</t>
+          <t>출산 후</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
-          <t>새벽 수유 때 물 온도 맞추는 시간이 확 줄어듭니다</t>
+          <t>2~3개월부터 필요</t>
         </is>
       </c>
     </row>
@@ -2012,17 +2028,17 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>보틀워머</t>
+          <t>젖꼭지 여분</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>3~5</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -2030,7 +2046,11 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G44" s="7" t="inlineStr"/>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>단계별로 교체해야 합니다</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
@@ -2045,29 +2065,25 @@
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>분유케이스</t>
+          <t>젖병솔 · 젖꼭지솔</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>1세트</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>36주</t>
-        </is>
-      </c>
-      <c r="G45" s="11" t="inlineStr">
-        <is>
-          <t>외출 시</t>
-        </is>
-      </c>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G45" s="11" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -2082,7 +2098,7 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>수유쿠션</t>
+          <t>젖병 세정제</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -2115,7 +2131,7 @@
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>수유등</t>
+          <t>젖병소독기</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
@@ -2123,9 +2139,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E47" s="8" t="inlineStr">
-        <is>
-          <t>보통</t>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
@@ -2133,11 +2149,7 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G47" s="11" t="inlineStr">
-        <is>
-          <t>새벽에 큰 불 켜면 아기가 깹니다</t>
-        </is>
-      </c>
+      <c r="G47" s="11" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -2152,7 +2164,7 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>분유제조기</t>
+          <t>젖병 건조대</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -2160,21 +2172,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E48" s="12" t="inlineStr">
-        <is>
-          <t>굳이</t>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G48" s="7" t="inlineStr">
-        <is>
-          <t>굳이템 상위. 세척이 번거로워 결국 안 씁니다</t>
-        </is>
-      </c>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
@@ -2189,25 +2197,29 @@
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>트림쿠션</t>
+          <t>분유</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E49" s="12" t="inlineStr">
-        <is>
-          <t>굳이</t>
+          <t>1~2</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G49" s="11" t="inlineStr"/>
+          <t>36주</t>
+        </is>
+      </c>
+      <c r="G49" s="11" t="inlineStr">
+        <is>
+          <t>조리원에서 먹던 걸로 준비해두고, 이후 필요에 따라 바꾸세요</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -2217,12 +2229,12 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>집 · 수면</t>
+          <t>집 · 수유</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>아기침대 or 범퍼침대</t>
+          <t>분유포트 (보온)</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -2237,12 +2249,12 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>32주</t>
+          <t>34주</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>6개월~1년이면 졸업</t>
+          <t>[직접 타는 방식] 분유쉐이커와 짝. 분유제조기를 쓸 거면 필요 없습니다</t>
         </is>
       </c>
     </row>
@@ -2254,32 +2266,32 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>집 · 수면</t>
+          <t>집 · 수유</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>매트리스 · 방수요</t>
+          <t>분유쉐이커</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>1~2</t>
-        </is>
-      </c>
-      <c r="E51" s="10" t="inlineStr">
-        <is>
-          <t>필수</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>32주</t>
+          <t>34주</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>방수요는 2장 이상 (밤에 갈아야 함)</t>
+          <t>[직접 타는 방식] 분유포트와 짝. 분유제조기를 쓸 거면 필요 없습니다</t>
         </is>
       </c>
     </row>
@@ -2291,30 +2303,34 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>집 · 수면</t>
+          <t>집 · 수유</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>침구세트</t>
+          <t>분유제조기</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1~2</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>필수</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>32주</t>
-        </is>
-      </c>
-      <c r="G52" s="7" t="inlineStr"/>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>[자동 방식] 이거 하나면 분유포트·쉐이커가 필요 없습니다. 다만 세척이 번거로워 결국 안 쓰게 됐다는 후기도 많아요</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
@@ -2324,22 +2340,22 @@
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>집 · 수면</t>
+          <t>집 · 수유</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>속싸개</t>
+          <t>보틀워머</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>3~4</t>
-        </is>
-      </c>
-      <c r="E53" s="10" t="inlineStr">
-        <is>
-          <t>필수</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
@@ -2347,11 +2363,7 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G53" s="11" t="inlineStr">
-        <is>
-          <t>생각보다 자주 갈아야 합니다</t>
-        </is>
-      </c>
+      <c r="G53" s="11" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -2361,17 +2373,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>집 · 수면</t>
+          <t>집 · 수유</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>스와들업</t>
+          <t>분유케이스</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -2381,12 +2393,12 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>34주</t>
+          <t>36주</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>모로반사 심한 아기에게</t>
+          <t>외출 시</t>
         </is>
       </c>
     </row>
@@ -2398,12 +2410,12 @@
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>집 · 수면</t>
+          <t>집 · 수유</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>백색소음기</t>
+          <t>수유쿠션</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
@@ -2421,7 +2433,11 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G55" s="11" t="inlineStr"/>
+      <c r="G55" s="11" t="inlineStr">
+        <is>
+          <t>모유수유할 때만 필요합니다</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -2431,30 +2447,34 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>집 · 수면</t>
+          <t>집 · 수유</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>아기 이불</t>
+          <t>수유등</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>필수</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>32주</t>
-        </is>
-      </c>
-      <c r="G56" s="7" t="inlineStr"/>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>새벽에 큰 불 켜면 아기가 깹니다</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
@@ -2464,32 +2484,32 @@
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>집 · 수면</t>
+          <t>집 · 수유</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>모빌</t>
+          <t>공갈 젖꼭지</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E57" s="12" t="inlineStr">
-        <is>
-          <t>굳이</t>
+          <t>2~3</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>36주</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
         <is>
-          <t>흥미를 금방 잃습니다</t>
+          <t>안 무는 아기도 있어서 1개 먼저 써보고 늘리세요</t>
         </is>
       </c>
     </row>
@@ -2501,30 +2521,34 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>집 · 목욕/위생</t>
+          <t>집 · 수유</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>아기 욕조</t>
+          <t>공갈 젖꼭지 집게 · 케이스</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>필수</t>
+          <t>1세트</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>34주</t>
-        </is>
-      </c>
-      <c r="G58" s="7" t="inlineStr"/>
+          <t>36주</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>외출 시 떨어뜨림 방지</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
@@ -2534,12 +2558,12 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>집 · 목욕/위생</t>
+          <t>집 · 수유</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>목욕 그물망 · 받침</t>
+          <t>젖병 집게</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
@@ -2559,7 +2583,7 @@
       </c>
       <c r="G59" s="11" t="inlineStr">
         <is>
-          <t>혼자 씻길 때 유용</t>
+          <t>소독 후 뜨거운 젖병 꺼낼 때</t>
         </is>
       </c>
     </row>
@@ -2571,22 +2595,22 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>집 · 목욕/위생</t>
+          <t>집 · 수유</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>세안타월 (가제)</t>
+          <t>젖병 보관함</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>20~30</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>필수</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -2596,7 +2620,7 @@
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>제일 많이 쓰는 물건. 넉넉히 준비하세요</t>
+          <t>먼지 차단</t>
         </is>
       </c>
     </row>
@@ -2608,30 +2632,34 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>집 · 목욕/위생</t>
+          <t>집 · 수유</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>큰 타월 (가운형)</t>
+          <t>모유 저장팩</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E61" s="10" t="inlineStr">
-        <is>
-          <t>필수</t>
+          <t>1팩</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>34주</t>
-        </is>
-      </c>
-      <c r="G61" s="11" t="inlineStr"/>
+          <t>36주</t>
+        </is>
+      </c>
+      <c r="G61" s="11" t="inlineStr">
+        <is>
+          <t>모유수유·유축하는 경우</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -2641,12 +2669,12 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>집 · 목욕/위생</t>
+          <t>집 · 수유</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>아기 워시 · 샴푸</t>
+          <t>수유 시트</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -2654,14 +2682,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>필수</t>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>34주</t>
+          <t>36주</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr"/>
@@ -2674,27 +2702,27 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>집 · 목욕/위생</t>
+          <t>집 · 수유</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>로션 · 크림</t>
+          <t>트림쿠션</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>1~2</t>
-        </is>
-      </c>
-      <c r="E63" s="10" t="inlineStr">
-        <is>
-          <t>필수</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E63" s="12" t="inlineStr">
+        <is>
+          <t>굳이</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>34주</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr"/>
@@ -2707,30 +2735,34 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>집 · 목욕/위생</t>
+          <t>집 · 수유</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>아기 손톱가위 · 면봉</t>
+          <t>수유 의자</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1세트</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>필수</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E64" s="12" t="inlineStr">
+        <is>
+          <t>굳이</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>34주</t>
-        </is>
-      </c>
-      <c r="G64" s="7" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>소파나 침대로 충분합니다</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
@@ -2740,12 +2772,12 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>집 · 목욕/위생</t>
+          <t>집 · 수유</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>체온계 (비접촉)</t>
+          <t>분유 디스펜서</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
@@ -2753,19 +2785,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E65" s="10" t="inlineStr">
-        <is>
-          <t>필수</t>
+      <c r="E65" s="12" t="inlineStr">
+        <is>
+          <t>굳이</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>34주</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
         <is>
-          <t>정확도가 판단 기준이 됩니다</t>
+          <t>외출이 잦아지면 그때 사도 됩니다</t>
         </is>
       </c>
     </row>
@@ -2777,32 +2809,32 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>집 · 목욕/위생</t>
+          <t>집 · 수면</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>배꼽소독 용품</t>
+          <t>아기침대 or 범퍼침대</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>1세트</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>필수</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>34주</t>
+          <t>32주</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>퇴원 직후 바로 씁니다</t>
+          <t>6개월~1년이면 졸업</t>
         </is>
       </c>
     </row>
@@ -2814,17 +2846,17 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>집 · 목욕/위생</t>
+          <t>집 · 수면</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>기저귀 (신생아용)</t>
+          <t>매트리스 · 방수요</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>1~2팩</t>
+          <t>1~2</t>
         </is>
       </c>
       <c r="E67" s="10" t="inlineStr">
@@ -2834,12 +2866,12 @@
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>36주</t>
+          <t>32주</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr">
         <is>
-          <t>사이즈가 금방 바뀝니다. 대량 구매 금물</t>
+          <t>방수요는 2장 이상 (밤에 갈아야 함)</t>
         </is>
       </c>
     </row>
@@ -2851,17 +2883,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>집 · 목욕/위생</t>
+          <t>집 · 수면</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>물티슈</t>
+          <t>침구세트</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>대량</t>
+          <t>1~2</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -2871,14 +2903,10 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>34주</t>
-        </is>
-      </c>
-      <c r="G68" s="7" t="inlineStr">
-        <is>
-          <t>이건 많이 사도 됩니다</t>
-        </is>
-      </c>
+          <t>32주</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
@@ -2888,22 +2916,22 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>집 · 목욕/위생</t>
+          <t>집 · 수면</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>기저귀 휴지통</t>
+          <t>속싸개</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E69" s="8" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>3~4</t>
+        </is>
+      </c>
+      <c r="E69" s="10" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
@@ -2911,7 +2939,11 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G69" s="11" t="inlineStr"/>
+      <c r="G69" s="11" t="inlineStr">
+        <is>
+          <t>생각보다 자주 갈아야 합니다</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -2921,17 +2953,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>집 · 목욕/위생</t>
+          <t>집 · 수면</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>엉덩이 세정기</t>
+          <t>스와들업</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
@@ -2944,7 +2976,11 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G70" s="7" t="inlineStr"/>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>모로반사 심한 아기에게</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
@@ -2954,12 +2990,12 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>집 · 목욕/위생</t>
+          <t>집 · 수면</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>아기 빗</t>
+          <t>백색소음기</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
@@ -2967,9 +3003,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E71" s="8" t="inlineStr">
-        <is>
-          <t>보통</t>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F71" s="8" t="inlineStr">
@@ -2987,32 +3023,32 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>집 · 목욕/위생</t>
+          <t>집 · 수면</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>콧물흡입기 (노시부)</t>
+          <t>아기 이불</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E72" s="12" t="inlineStr">
-        <is>
-          <t>굳이</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>32주</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>신생아 때는 거의 안 씁니다. 아플 때 사도 늦지 않아요</t>
+          <t>질식 위험이 있어 이불 사용은 권장하지 않습니다. 이불보다 집 온도를 맞춰주세요</t>
         </is>
       </c>
     </row>
@@ -3024,12 +3060,12 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>집 · 목욕/위생</t>
+          <t>집 · 수면</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>기저귀 갈이대</t>
+          <t>암막 커튼</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
@@ -3037,19 +3073,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E73" s="12" t="inlineStr">
-        <is>
-          <t>굳이</t>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>32주</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
         <is>
-          <t>바닥이나 침대에서 갈게 됩니다</t>
+          <t>낮잠 재울 때 차이가 큽니다</t>
         </is>
       </c>
     </row>
@@ -3061,22 +3097,22 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>집 · 의류</t>
+          <t>집 · 수면</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>배냇저고리</t>
+          <t>모로반사 방지 (토닥슈트 등)</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>3~5</t>
-        </is>
-      </c>
-      <c r="E74" s="6" t="inlineStr">
-        <is>
-          <t>필수</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -3084,7 +3120,11 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G74" s="7" t="inlineStr"/>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>속싸개·스와들업으로 안 되면</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
@@ -3094,34 +3134,30 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>집 · 의류</t>
+          <t>집 · 수면</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>바디슈트 · 우주복</t>
+          <t>침대 맞춤 패드</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>5~7</t>
-        </is>
-      </c>
-      <c r="E75" s="10" t="inlineStr">
-        <is>
-          <t>필수</t>
+          <t>1~2</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>34주</t>
-        </is>
-      </c>
-      <c r="G75" s="11" t="inlineStr">
-        <is>
-          <t>신생아 사이즈는 한 달이면 끝납니다</t>
-        </is>
-      </c>
+          <t>32주</t>
+        </is>
+      </c>
+      <c r="G75" s="11" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -3131,17 +3167,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>집 · 의류</t>
+          <t>집 · 수면</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>손싸개 · 발싸개</t>
+          <t>거즈 블랭킷</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>2~3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
@@ -3154,7 +3190,11 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G76" s="7" t="inlineStr"/>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>덮개 겸 햇빛 가리개</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
@@ -3164,30 +3204,34 @@
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>집 · 의류</t>
+          <t>집 · 수면</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>턱받이</t>
+          <t>모빌</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E77" s="8" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E77" s="12" t="inlineStr">
+        <is>
+          <t>굳이</t>
         </is>
       </c>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>출산 후</t>
-        </is>
-      </c>
-      <c r="G77" s="11" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G77" s="11" t="inlineStr">
+        <is>
+          <t>흥미를 금방 잃습니다</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -3197,30 +3241,34 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>집 · 의류</t>
+          <t>집 · 수면</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>신생아 양말</t>
+          <t>태열베개 · 짱구베개</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>3~5</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E78" s="12" t="inlineStr">
+        <is>
+          <t>굳이</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>34주</t>
-        </is>
-      </c>
-      <c r="G78" s="7" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>뒤집기 시작하면 안전 문제로 못 씁니다 (4~6개월)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
@@ -3230,12 +3278,12 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>집 · 의류</t>
+          <t>집 · 수면</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>아기 전용 세제</t>
+          <t>바디필로우</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
@@ -3243,17 +3291,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E79" s="10" t="inlineStr">
-        <is>
-          <t>필수</t>
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t>굳이</t>
         </is>
       </c>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>34주</t>
-        </is>
-      </c>
-      <c r="G79" s="11" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G79" s="11" t="inlineStr">
+        <is>
+          <t>역방쿠·수유시트가 있으면 잘 안 씁니다</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -3263,34 +3315,30 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>집 · 의류</t>
+          <t>집 · 목욕/위생</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>신생아 신발</t>
+          <t>아기 욕조</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E80" s="12" t="inlineStr">
-        <is>
-          <t>굳이</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G80" s="7" t="inlineStr">
-        <is>
-          <t>걷기 전엔 사진용입니다</t>
-        </is>
-      </c>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
@@ -3300,17 +3348,17 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>집 · 외출</t>
+          <t>집 · 목욕/위생</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>카시트</t>
+          <t>가제 손수건</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20~30</t>
         </is>
       </c>
       <c r="E81" s="10" t="inlineStr">
@@ -3320,12 +3368,12 @@
       </c>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>32주</t>
+          <t>34주</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr">
         <is>
-          <t>중고 금지 — 사고 이력 확인 불가</t>
+          <t>아주 부드러워서 얼굴·입 안처럼 자극이 적어야 하는 곳에 씁니다. 제일 많이 쓰는 물건이에요</t>
         </is>
       </c>
     </row>
@@ -3337,17 +3385,17 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>집 · 외출</t>
+          <t>집 · 목욕/위생</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>유모차</t>
+          <t>엠보 손수건</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10~20</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -3357,12 +3405,12 @@
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>32주</t>
+          <t>34주</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>디럭스/절충형 미리 비교해두세요</t>
+          <t>가제보다 아주 조금 거칩니다. 엉덩이·팔 등 얼굴 외에 씁니다</t>
         </is>
       </c>
     </row>
@@ -3374,17 +3422,17 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>집 · 외출</t>
+          <t>집 · 목욕/위생</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>아기띠</t>
+          <t>샤워 타월 (또는 천기저귀)</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E83" s="10" t="inlineStr">
@@ -3399,7 +3447,7 @@
       </c>
       <c r="G83" s="11" t="inlineStr">
         <is>
-          <t>신생아용 인서트 확인</t>
+          <t>목욕 후에 씁니다</t>
         </is>
       </c>
     </row>
@@ -3411,12 +3459,12 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>집 · 외출</t>
+          <t>집 · 목욕/위생</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>기저귀 가방</t>
+          <t>아기 워시 · 샴푸</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -3424,21 +3472,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>보통</t>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>36주</t>
-        </is>
-      </c>
-      <c r="G84" s="7" t="inlineStr">
-        <is>
-          <t>에코백으로 대체 가능</t>
-        </is>
-      </c>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
@@ -3448,27 +3492,27 @@
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>집 · 외출</t>
+          <t>집 · 목욕/위생</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>휴대용 기저귀 매트</t>
+          <t>로션 · 크림</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E85" s="8" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>1~2</t>
+        </is>
+      </c>
+      <c r="E85" s="10" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F85" s="8" t="inlineStr">
         <is>
-          <t>36주</t>
+          <t>34주</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr"/>
@@ -3481,12 +3525,12 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>집 · 외출</t>
+          <t>집 · 목욕/위생</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>유모차 방한 · 방수커버</t>
+          <t>기저귀 크림</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -3494,19 +3538,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>보통</t>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>계절 맞춰</t>
+          <t>34주</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>겨울 출산이면 미리 준비</t>
+          <t>기저귀 발진은 거의 반드시 옵니다</t>
         </is>
       </c>
     </row>
@@ -3518,12 +3562,12 @@
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>집 · 기타</t>
+          <t>집 · 목욕/위생</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>가습기</t>
+          <t>판테놀 연고</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
@@ -3543,7 +3587,7 @@
       </c>
       <c r="G87" s="11" t="inlineStr">
         <is>
-          <t>겨울 출산이면 필수에 가깝습니다</t>
+          <t>발진·트러블 났을 때. 약국에서 삽니다</t>
         </is>
       </c>
     </row>
@@ -3555,12 +3599,12 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>집 · 기타</t>
+          <t>집 · 목욕/위생</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>공기청정기</t>
+          <t>아기 오일</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -3575,10 +3619,14 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G88" s="7" t="inlineStr"/>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>태열·각질 관리</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
@@ -3588,12 +3636,12 @@
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>집 · 기타</t>
+          <t>집 · 목욕/위생</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>온습도계</t>
+          <t>탕온도계</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
@@ -3613,7 +3661,7 @@
       </c>
       <c r="G89" s="11" t="inlineStr">
         <is>
-          <t>아기방 온도 22~24도 / 습도 50~60%</t>
+          <t>목욕물 37~38도. 손 감각은 생각보다 부정확합니다</t>
         </is>
       </c>
     </row>
@@ -3625,12 +3673,12 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>집 · 기타</t>
+          <t>집 · 목욕/위생</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>손소독제</t>
+          <t>샴푸 헤어캡</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -3650,7 +3698,7 @@
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>방문객용</t>
+          <t>눈에 물 안 들어가게</t>
         </is>
       </c>
     </row>
@@ -3662,17 +3710,17 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>집 · 기타</t>
+          <t>집 · 목욕/위생</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>수유일지 (앱/노트)</t>
+          <t>소독 티슈 · 제균 스프레이</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1세트</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
@@ -3682,12 +3730,12 @@
       </c>
       <c r="F91" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>34주</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr">
         <is>
-          <t>수유텀·배변 기록. 병원 갈 때 도움됨</t>
+          <t>장난감·바닥용</t>
         </is>
       </c>
     </row>
@@ -3699,30 +3747,34 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>집 · 기타</t>
+          <t>집 · 목욕/위생</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>산모 영양제 (철분·유산균)</t>
+          <t>지퍼백</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E92" s="6" t="inlineStr">
-        <is>
-          <t>필수</t>
+          <t>1팩</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G92" s="7" t="inlineStr"/>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>물티슈 덜어 담기, 외출용 소분</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
@@ -3732,34 +3784,30 @@
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>집 · 기타</t>
+          <t>집 · 목욕/위생</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>아기체육관 · 플레이매트</t>
+          <t>아기 손톱가위 · 면봉</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E93" s="8" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>1세트</t>
+        </is>
+      </c>
+      <c r="E93" s="10" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F93" s="8" t="inlineStr">
         <is>
-          <t>출산 후</t>
-        </is>
-      </c>
-      <c r="G93" s="11" t="inlineStr">
-        <is>
-          <t>3개월 이후에 사도 됩니다</t>
-        </is>
-      </c>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G93" s="11" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -3769,12 +3817,12 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>집 · 기타</t>
+          <t>집 · 목욕/위생</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>바운서</t>
+          <t>체온계</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -3782,21 +3830,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E94" s="12" t="inlineStr">
-        <is>
-          <t>굳이</t>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G94" s="7" t="inlineStr">
-        <is>
-          <t>안 타는 아기가 많습니다. 중고로 먼저 시도</t>
-        </is>
-      </c>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G94" s="7" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
@@ -3806,30 +3850,34 @@
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>집 · 기타</t>
+          <t>집 · 목욕/위생</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>역류방지쿠션</t>
+          <t>배꼽소독 용품</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E95" s="12" t="inlineStr">
-        <is>
-          <t>굳이</t>
+          <t>1세트</t>
+        </is>
+      </c>
+      <c r="E95" s="10" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F95" s="8" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G95" s="11" t="inlineStr"/>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G95" s="11" t="inlineStr">
+        <is>
+          <t>퇴원 직후 바로 씁니다</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
@@ -3839,32 +3887,32 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>집 · 기타</t>
+          <t>집 · 목욕/위생</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>아기 체중계</t>
+          <t>기저귀 (신생아용)</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E96" s="12" t="inlineStr">
-        <is>
-          <t>굳이</t>
+          <t>1~2팩</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>36주</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>병원·보건소에서 잽니다</t>
+          <t>사이즈가 금방 바뀝니다. 대량 구매 금물</t>
         </is>
       </c>
     </row>
@@ -3876,32 +3924,32 @@
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>집 · 기타</t>
+          <t>집 · 목욕/위생</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>열탕소독기</t>
+          <t>물티슈</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E97" s="12" t="inlineStr">
-        <is>
-          <t>굳이</t>
+          <t>대량</t>
+        </is>
+      </c>
+      <c r="E97" s="10" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F97" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>34주</t>
         </is>
       </c>
       <c r="G97" s="11" t="inlineStr">
         <is>
-          <t>냄비로 충분합니다</t>
+          <t>이건 많이 사도 됩니다</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3961,12 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>집 · 기타</t>
+          <t>집 · 목욕/위생</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>젖병 건조 트레이</t>
+          <t>기저귀 휴지통</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
@@ -3936,7 +3984,11 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G98" s="7" t="inlineStr"/>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>밀폐력만 좋으면 충분합니다</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
@@ -3946,17 +3998,17 @@
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>집 · 기타</t>
+          <t>집 · 목욕/위생</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>아기 손수건 (가제)</t>
+          <t>아기 비데</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>20~30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E99" s="10" t="inlineStr">
@@ -3971,7 +4023,7 @@
       </c>
       <c r="G99" s="11" t="inlineStr">
         <is>
-          <t>아무리 많아도 부족합니다</t>
+          <t>엄마 손목 지킴이입니다</t>
         </is>
       </c>
     </row>
@@ -3983,30 +4035,34 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>집 · 기타</t>
+          <t>집 · 목욕/위생</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>방수요 (여분)</t>
+          <t>콧물흡입기 (노시부)</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E100" s="6" t="inlineStr">
-        <is>
-          <t>필수</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E100" s="12" t="inlineStr">
+        <is>
+          <t>굳이</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>34주</t>
-        </is>
-      </c>
-      <c r="G100" s="7" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>신생아 때는 거의 안 씁니다. 아플 때 사도 늦지 않아요</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
@@ -4016,32 +4072,32 @@
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>집 · 기타</t>
+          <t>집 · 목욕/위생</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>유축기 개인부품</t>
+          <t>기저귀 갈이대</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>1세트</t>
-        </is>
-      </c>
-      <c r="E101" s="8" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="inlineStr">
+        <is>
+          <t>굳이</t>
         </is>
       </c>
       <c r="F101" s="8" t="inlineStr">
         <is>
-          <t>36주</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G101" s="11" t="inlineStr">
         <is>
-          <t>대여 시 부품만 새로 구매</t>
+          <t>바닥이나 침대에서 갈게 됩니다</t>
         </is>
       </c>
     </row>
@@ -4053,22 +4109,22 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>집 · 기타</t>
+          <t>집 · 의류</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>아기 손톱 줄 (파일)</t>
+          <t>배냇저고리</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
@@ -4076,11 +4132,7 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G102" s="7" t="inlineStr">
-        <is>
-          <t>가위가 무서우면 이걸로</t>
-        </is>
-      </c>
+      <c r="G102" s="7" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
@@ -4090,37 +4142,1588 @@
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
+          <t>집 · 의류</t>
+        </is>
+      </c>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>바디슈트 · 우주복</t>
+        </is>
+      </c>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t>5~7</t>
+        </is>
+      </c>
+      <c r="E103" s="10" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="F103" s="8" t="inlineStr">
+        <is>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G103" s="11" t="inlineStr">
+        <is>
+          <t>신생아 사이즈는 한 달이면 끝납니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>집 · 의류</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>손싸개 · 발싸개</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>2~3</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G104" s="7" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t>집 · 의류</t>
+        </is>
+      </c>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>턱받이</t>
+        </is>
+      </c>
+      <c r="D105" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="F105" s="8" t="inlineStr">
+        <is>
+          <t>출산 후</t>
+        </is>
+      </c>
+      <c r="G105" s="11" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>집 · 의류</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>신생아 양말</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>3~5</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>집 · 의류</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>배냇수트 (반팔·긴팔)</t>
+        </is>
+      </c>
+      <c r="D107" s="8" t="inlineStr">
+        <is>
+          <t>2~3</t>
+        </is>
+      </c>
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="F107" s="8" t="inlineStr">
+        <is>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G107" s="11" t="inlineStr">
+        <is>
+          <t>배냇저고리 다음 단계</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>집 · 의류</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>내복</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>2~3</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>출산 후</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>우주복 안에 입힙니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>집 · 의류</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>아기 전용 세제</t>
+        </is>
+      </c>
+      <c r="D109" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E109" s="10" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="F109" s="8" t="inlineStr">
+        <is>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G109" s="11" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>집 · 의류</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>무형광 세탁망</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G110" s="7" t="inlineStr">
+        <is>
+          <t>아기 옷은 따로 세탁합니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t>집 · 의류</t>
+        </is>
+      </c>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>아기 옷걸이</t>
+        </is>
+      </c>
+      <c r="D111" s="8" t="inlineStr">
+        <is>
+          <t>1세트</t>
+        </is>
+      </c>
+      <c r="E111" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="F111" s="8" t="inlineStr">
+        <is>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G111" s="11" t="inlineStr">
+        <is>
+          <t>어른 옷걸이엔 안 걸립니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>집 · 의류</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>신생아 신발</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E112" s="12" t="inlineStr">
+        <is>
+          <t>굳이</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G112" s="7" t="inlineStr">
+        <is>
+          <t>걷기 전엔 사진용입니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B113" s="9" t="inlineStr">
+        <is>
+          <t>집 · 외출</t>
+        </is>
+      </c>
+      <c r="C113" s="9" t="inlineStr">
+        <is>
+          <t>카시트</t>
+        </is>
+      </c>
+      <c r="D113" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E113" s="10" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="F113" s="8" t="inlineStr">
+        <is>
+          <t>32주</t>
+        </is>
+      </c>
+      <c r="G113" s="11" t="inlineStr">
+        <is>
+          <t>중고 금지 — 사고 이력 확인 불가</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>집 · 외출</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>유모차</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>32주</t>
+        </is>
+      </c>
+      <c r="G114" s="7" t="inlineStr">
+        <is>
+          <t>디럭스/절충형 미리 비교해두세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B115" s="9" t="inlineStr">
+        <is>
+          <t>집 · 외출</t>
+        </is>
+      </c>
+      <c r="C115" s="9" t="inlineStr">
+        <is>
+          <t>아기띠</t>
+        </is>
+      </c>
+      <c r="D115" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E115" s="10" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="F115" s="8" t="inlineStr">
+        <is>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G115" s="11" t="inlineStr">
+        <is>
+          <t>신생아용 인서트 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>집 · 외출</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>카시트 후방거울</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G116" s="7" t="inlineStr">
+        <is>
+          <t>운전 중 아기 상태 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B117" s="9" t="inlineStr">
+        <is>
+          <t>집 · 외출</t>
+        </is>
+      </c>
+      <c r="C117" s="9" t="inlineStr">
+        <is>
+          <t>유모차 가리개 · 라이너</t>
+        </is>
+      </c>
+      <c r="D117" s="8" t="inlineStr">
+        <is>
+          <t>1세트</t>
+        </is>
+      </c>
+      <c r="E117" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="F117" s="8" t="inlineStr">
+        <is>
+          <t>36주</t>
+        </is>
+      </c>
+      <c r="G117" s="11" t="inlineStr">
+        <is>
+          <t>햇빛·계절 대응</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>집 · 외출</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>기저귀 가방</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>36주</t>
+        </is>
+      </c>
+      <c r="G118" s="7" t="inlineStr">
+        <is>
+          <t>에코백으로 대체 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B119" s="9" t="inlineStr">
+        <is>
+          <t>집 · 외출</t>
+        </is>
+      </c>
+      <c r="C119" s="9" t="inlineStr">
+        <is>
+          <t>휴대용 기저귀 매트</t>
+        </is>
+      </c>
+      <c r="D119" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E119" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="F119" s="8" t="inlineStr">
+        <is>
+          <t>36주</t>
+        </is>
+      </c>
+      <c r="G119" s="11" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>집 · 외출</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>유모차 방한 · 방수커버</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>계절 맞춰</t>
+        </is>
+      </c>
+      <c r="G120" s="7" t="inlineStr">
+        <is>
+          <t>겨울 출산이면 미리 준비</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B121" s="9" t="inlineStr">
+        <is>
           <t>집 · 기타</t>
         </is>
       </c>
-      <c r="C103" s="9" t="inlineStr">
+      <c r="C121" s="9" t="inlineStr">
+        <is>
+          <t>가습기</t>
+        </is>
+      </c>
+      <c r="D121" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E121" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="F121" s="8" t="inlineStr">
+        <is>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G121" s="11" t="inlineStr">
+        <is>
+          <t>겨울 출산이면 필수에 가깝습니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>집 · 기타</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>공기청정기</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G122" s="7" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B123" s="9" t="inlineStr">
+        <is>
+          <t>집 · 기타</t>
+        </is>
+      </c>
+      <c r="C123" s="9" t="inlineStr">
+        <is>
+          <t>온습도계</t>
+        </is>
+      </c>
+      <c r="D123" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E123" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="F123" s="8" t="inlineStr">
+        <is>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G123" s="11" t="inlineStr">
+        <is>
+          <t>아기방 온도 22~24도 / 습도 50~60%</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>집 · 기타</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>손소독제</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G124" s="7" t="inlineStr">
+        <is>
+          <t>방문객용</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B125" s="9" t="inlineStr">
+        <is>
+          <t>집 · 기타</t>
+        </is>
+      </c>
+      <c r="C125" s="9" t="inlineStr">
+        <is>
+          <t>수유일지 (앱/노트)</t>
+        </is>
+      </c>
+      <c r="D125" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E125" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="F125" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G125" s="11" t="inlineStr">
+        <is>
+          <t>수유텀·배변 기록. 병원 갈 때 도움됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>집 · 기타</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>산모 영양제 (철분·유산균)</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E126" s="6" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G126" s="7" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B127" s="9" t="inlineStr">
+        <is>
+          <t>집 · 기타</t>
+        </is>
+      </c>
+      <c r="C127" s="9" t="inlineStr">
+        <is>
+          <t>아기체육관 · 플레이매트</t>
+        </is>
+      </c>
+      <c r="D127" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E127" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="F127" s="8" t="inlineStr">
+        <is>
+          <t>출산 후</t>
+        </is>
+      </c>
+      <c r="G127" s="11" t="inlineStr">
+        <is>
+          <t>3개월 이후에 사도 됩니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>집 · 기타</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>바운서</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E128" s="12" t="inlineStr">
+        <is>
+          <t>굳이</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G128" s="7" t="inlineStr">
+        <is>
+          <t>안 타는 아기가 많습니다. 중고로 먼저 시도</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B129" s="9" t="inlineStr">
+        <is>
+          <t>집 · 기타</t>
+        </is>
+      </c>
+      <c r="C129" s="9" t="inlineStr">
+        <is>
+          <t>역류방지쿠션</t>
+        </is>
+      </c>
+      <c r="D129" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E129" s="12" t="inlineStr">
+        <is>
+          <t>굳이</t>
+        </is>
+      </c>
+      <c r="F129" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G129" s="11" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>집 · 기타</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>아기 체중계</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E130" s="12" t="inlineStr">
+        <is>
+          <t>굳이</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G130" s="7" t="inlineStr">
+        <is>
+          <t>병원·보건소에서 잽니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B131" s="9" t="inlineStr">
+        <is>
+          <t>집 · 기타</t>
+        </is>
+      </c>
+      <c r="C131" s="9" t="inlineStr">
+        <is>
+          <t>열탕소독기</t>
+        </is>
+      </c>
+      <c r="D131" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E131" s="12" t="inlineStr">
+        <is>
+          <t>굳이</t>
+        </is>
+      </c>
+      <c r="F131" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G131" s="11" t="inlineStr">
+        <is>
+          <t>냄비로 충분합니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>집 · 기타</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>젖병 건조 트레이</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G132" s="7" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B133" s="9" t="inlineStr">
+        <is>
+          <t>집 · 기타</t>
+        </is>
+      </c>
+      <c r="C133" s="9" t="inlineStr">
+        <is>
+          <t>방수요 (여분)</t>
+        </is>
+      </c>
+      <c r="D133" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E133" s="10" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="F133" s="8" t="inlineStr">
+        <is>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G133" s="11" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>집 · 기타</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>유축기 개인부품</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>1세트</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>36주</t>
+        </is>
+      </c>
+      <c r="G134" s="7" t="inlineStr">
+        <is>
+          <t>대여 시 부품만 새로 구매</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B135" s="9" t="inlineStr">
+        <is>
+          <t>집 · 기타</t>
+        </is>
+      </c>
+      <c r="C135" s="9" t="inlineStr">
+        <is>
+          <t>아기 손톱 줄 (파일)</t>
+        </is>
+      </c>
+      <c r="D135" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E135" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="F135" s="8" t="inlineStr">
+        <is>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G135" s="11" t="inlineStr">
+        <is>
+          <t>가위가 무서우면 이걸로</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>집 · 기타</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
         <is>
           <t>수유 시간 알람 (앱)</t>
         </is>
       </c>
-      <c r="D103" s="8" t="inlineStr">
+      <c r="D136" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E103" s="8" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="F103" s="8" t="inlineStr">
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="F136" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G103" s="11" t="inlineStr">
+      <c r="G136" s="7" t="inlineStr">
         <is>
           <t>2~3시간 간격, 처음엔 놓치기 쉽습니다</t>
         </is>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B137" s="9" t="inlineStr">
+        <is>
+          <t>집 · 기타</t>
+        </is>
+      </c>
+      <c r="C137" s="9" t="inlineStr">
+        <is>
+          <t>제습기</t>
+        </is>
+      </c>
+      <c r="D137" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E137" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="F137" s="8" t="inlineStr">
+        <is>
+          <t>계절 맞춰</t>
+        </is>
+      </c>
+      <c r="G137" s="11" t="inlineStr">
+        <is>
+          <t>여름 출산이면</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>집 · 기타</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>대형 빨래 건조대</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G138" s="7" t="inlineStr">
+        <is>
+          <t>아기 빨래가 매일 나옵니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B139" s="9" t="inlineStr">
+        <is>
+          <t>집 · 기타</t>
+        </is>
+      </c>
+      <c r="C139" s="9" t="inlineStr">
+        <is>
+          <t>아기 수납장 · 서랍장</t>
+        </is>
+      </c>
+      <c r="D139" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E139" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="F139" s="8" t="inlineStr">
+        <is>
+          <t>32주</t>
+        </is>
+      </c>
+      <c r="G139" s="11" t="inlineStr">
+        <is>
+          <t>기저귀·옷 정리용</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>집 · 기타</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>기저귀 트롤리</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G140" s="7" t="inlineStr">
+        <is>
+          <t>갈이대 옆에 두고 씁니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B141" s="9" t="inlineStr">
+        <is>
+          <t>집 · 기타</t>
+        </is>
+      </c>
+      <c r="C141" s="9" t="inlineStr">
+        <is>
+          <t>흑백 초점책</t>
+        </is>
+      </c>
+      <c r="D141" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E141" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="F141" s="8" t="inlineStr">
+        <is>
+          <t>출산 후</t>
+        </is>
+      </c>
+      <c r="G141" s="11" t="inlineStr">
+        <is>
+          <t>신생아 시력 발달용. 3개월 내외까지</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>집 · 기타</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>거실 매트</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>출산 후</t>
+        </is>
+      </c>
+      <c r="G142" s="7" t="inlineStr">
+        <is>
+          <t>기기 시작할 때. 미리 안 사도 됩니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B143" s="9" t="inlineStr">
+        <is>
+          <t>집 · 기타</t>
+        </is>
+      </c>
+      <c r="C143" s="9" t="inlineStr">
+        <is>
+          <t>범보의자</t>
+        </is>
+      </c>
+      <c r="D143" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E143" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="F143" s="8" t="inlineStr">
+        <is>
+          <t>출산 후</t>
+        </is>
+      </c>
+      <c r="G143" s="11" t="inlineStr">
+        <is>
+          <t>앉기 연습용. 3~6개월부터</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>집 · 기타</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>초음파 · 주사 앨범</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
+        </is>
+      </c>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G144" s="7" t="inlineStr">
+        <is>
+          <t>기록용</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="8" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B145" s="9" t="inlineStr">
+        <is>
+          <t>집 · 기타</t>
+        </is>
+      </c>
+      <c r="C145" s="9" t="inlineStr">
+        <is>
+          <t>아기 전용 세탁기</t>
+        </is>
+      </c>
+      <c r="D145" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E145" s="12" t="inlineStr">
+        <is>
+          <t>굳이</t>
+        </is>
+      </c>
+      <c r="F145" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G145" s="11" t="inlineStr">
+        <is>
+          <t>일반 세탁기 + 아기 세제로 충분합니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>집 · 기타</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t>아기 수영장 · 목튜브</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E146" s="12" t="inlineStr">
+        <is>
+          <t>굳이</t>
+        </is>
+      </c>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G146" s="7" t="inlineStr">
+        <is>
+          <t>100일 전후 잠깐 이벤트용</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:G103"/>
+  <autoFilter ref="A3:G146"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/baby/posts/20260807-noti-checklist/files/출산준비물_체크리스트_보아르아가노트.xlsx
+++ b/baby/posts/20260807-noti-checklist/files/출산준비물_체크리스트_보아르아가노트.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="읽어주세요" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'출산준비물 체크리스트'!$A$3:$G$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'출산준비물 체크리스트'!$A$3:$G$139</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G146"/>
+  <dimension ref="A1:G139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -543,7 +543,7 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>출산 준비물 체크리스트  ·  총 143개</t>
+          <t>출산 준비물 체크리스트  ·  총 136개</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>신분증 · 산모수첩 · 보험증서</t>
+          <t>신분증 · 산모수첩</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>분만실이 많이 춥습니다</t>
+          <t>출산 이후엔 몸을 따뜻하게 해야 합니다</t>
         </is>
       </c>
     </row>
@@ -1217,9 +1217,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
-        <is>
-          <t>필수</t>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>젖몸살은 거의 모두 겪습니다. 손수건에 둘러서 쓰세요</t>
+          <t>조리원에서 아이스팩을 제공한다면 굳이 안 사도 됩니다</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>산모 치약</t>
+          <t>압박스타킹</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>시린 이가 생기는 경우가 많습니다</t>
+          <t>부기 완화용</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>병원 · 산모</t>
+          <t>병원 · 아기</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>압박스타킹</t>
+          <t>배냇저고리</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -1291,9 +1291,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>보통</t>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>부기 완화용</t>
+          <t>퇴원 때 입힐 것</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>배냇저고리</t>
+          <t>아기 바지</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>퇴원 때 입힐 것</t>
+          <t>집에 갈 때 카시트를 태워야 하는데, 바지가 없으면 맨다리가 됩니다</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>아기 바지</t>
+          <t>속싸개</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -1375,11 +1375,7 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G25" s="11" t="inlineStr">
-        <is>
-          <t>집에 갈 때 카시트를 태워야 하는데, 바지가 없으면 맨다리가 됩니다</t>
-        </is>
-      </c>
+      <c r="G25" s="11" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -1394,12 +1390,12 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>속싸개</t>
+          <t>겉싸개</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>1~2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -1412,7 +1408,11 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G26" s="7" t="inlineStr"/>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>계절 맞춰서</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>겉싸개</t>
+          <t>손싸개 · 아기모자</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E27" s="10" t="inlineStr">
-        <is>
-          <t>필수</t>
+          <t>1세트</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
@@ -1445,11 +1445,7 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
-        <is>
-          <t>계절 맞춰서</t>
-        </is>
-      </c>
+      <c r="G27" s="11" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -1464,17 +1460,17 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>손싸개 · 아기모자</t>
+          <t>가제손수건</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>1세트</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -1497,12 +1493,12 @@
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>가제손수건</t>
+          <t>아기 유산균</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
@@ -1512,10 +1508,14 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>34주</t>
-        </is>
-      </c>
-      <c r="G29" s="11" t="inlineStr"/>
+          <t>36주</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>조리원에 맡기면 하루 한 번 먹여줍니다. 요즘은 비타민D가 포함된 제품(바이오가이아 이지드롭 등)을 많이 씁니다</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>아기 유산균</t>
+          <t>신생아 카시트</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>36주</t>
+          <t>32주</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>조리원에 맡기면 하루 한 번 먹여줍니다. 요즘은 비타민D가 포함된 제품(바이오가이아 이지드롭 등)을 많이 씁니다</t>
+          <t>퇴원 시 반드시 필요. 중고 절대 비추</t>
         </is>
       </c>
     </row>
@@ -1562,17 +1562,17 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>병원 · 아기</t>
+          <t>조리원</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>신생아 카시트</t>
+          <t>편한 옷 (수유 가능)</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3~4</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>32주</t>
+          <t>36주</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>퇴원 시 반드시 필요. 중고 절대 비추</t>
+          <t>앞트임 필수</t>
         </is>
       </c>
     </row>
@@ -1604,12 +1604,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>편한 옷 (수유 가능)</t>
+          <t>개인 세면도구</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>3~4</t>
+          <t>1세트</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -1622,11 +1622,7 @@
           <t>36주</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>앞트임 필수</t>
-        </is>
-      </c>
+      <c r="G32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
@@ -1641,12 +1637,12 @@
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>개인 세면도구</t>
+          <t>콘센트 (멀티탭)</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>1세트</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
@@ -1659,7 +1655,11 @@
           <t>36주</t>
         </is>
       </c>
-      <c r="G33" s="11" t="inlineStr"/>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>침대 주변 콘센트가 부족합니다</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>콘센트 (멀티탭)</t>
+          <t>수유쿠션</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -1682,19 +1682,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>필수</t>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>굳이</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>36주</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>침대 주변 콘센트가 부족합니다</t>
+          <t>요즘 조리원엔 대부분 비치돼 있습니다. 미리 확인해보세요</t>
         </is>
       </c>
     </row>
@@ -1711,12 +1711,12 @@
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>수유쿠션</t>
+          <t>깔대기</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1세트</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
-          <t>요즘 조리원엔 대부분 비치돼 있습니다. 미리 확인해보세요</t>
+          <t>유축기는 보건소·조리원에서 무료 대여됩니다. 깔대기는 조리원에서 구매하세요</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>유축기</t>
+          <t>튼살크림</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -1763,14 +1763,10 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>36주</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>보건소 무료 대여 가능. 개인부품만 구매</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
@@ -1785,7 +1781,7 @@
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>젖병 세정제</t>
+          <t>노트북 · 태블릿</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -1793,17 +1789,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E37" s="10" t="inlineStr">
-        <is>
-          <t>필수</t>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>34주</t>
-        </is>
-      </c>
-      <c r="G37" s="11" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>생각보다 시간이 많습니다</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>튼살크림</t>
+          <t>산모용 슬리퍼</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1826,14 +1826,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>보통</t>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>36주</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr"/>
@@ -1846,32 +1846,32 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>조리원</t>
+          <t>집 · 수유</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>노트북 · 태블릿</t>
+          <t>젖병 (신생아 소용량)</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>3~5</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>34주</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
-          <t>생각보다 시간이 많습니다</t>
+          <t>처음부터 많이 사지 말고 아기 반응 보고 추가</t>
         </is>
       </c>
     </row>
@@ -1883,30 +1883,34 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>조리원</t>
+          <t>집 · 수유</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>산모용 슬리퍼</t>
+          <t>젖병 (중용량)</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>필수</t>
+          <t>3~5</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>36주</t>
-        </is>
-      </c>
-      <c r="G40" s="7" t="inlineStr"/>
+          <t>출산 후</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>2~3개월부터 필요</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -1916,30 +1920,34 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>조리원</t>
+          <t>집 · 수유</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>간식 · 보리차</t>
+          <t>젖꼭지 여분</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>3~5</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G41" s="11" t="inlineStr"/>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>단계별로 교체해야 합니다</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -1954,12 +1962,12 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>젖병 (신생아 소용량)</t>
+          <t>젖병솔 · 젖꼭지솔</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>3~5</t>
+          <t>1세트</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -1972,11 +1980,7 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G42" s="7" t="inlineStr">
-        <is>
-          <t>처음부터 많이 사지 말고 아기 반응 보고 추가</t>
-        </is>
-      </c>
+      <c r="G42" s="7" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -1991,29 +1995,25 @@
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>젖병 (중용량)</t>
+          <t>젖병 세정제</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>3~5</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>출산 후</t>
-        </is>
-      </c>
-      <c r="G43" s="11" t="inlineStr">
-        <is>
-          <t>2~3개월부터 필요</t>
-        </is>
-      </c>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G43" s="11" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -2028,12 +2028,12 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>젖꼭지 여분</t>
+          <t>젖병소독기</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>3~5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -2046,11 +2046,7 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>단계별로 교체해야 합니다</t>
-        </is>
-      </c>
+      <c r="G44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
@@ -2065,17 +2061,17 @@
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>젖병솔 · 젖꼭지솔</t>
+          <t>젖병 건조대</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>1세트</t>
-        </is>
-      </c>
-      <c r="E45" s="10" t="inlineStr">
-        <is>
-          <t>필수</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
@@ -2098,12 +2094,12 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>젖병 세정제</t>
+          <t>분유</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1~2</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -2113,10 +2109,14 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>34주</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="inlineStr"/>
+          <t>36주</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>조리원에서 먹던 걸로 준비해두고, 이후 필요에 따라 바꾸세요</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>젖병소독기</t>
+          <t>분유포트 (보온)</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
@@ -2139,9 +2139,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E47" s="10" t="inlineStr">
-        <is>
-          <t>필수</t>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
@@ -2149,7 +2149,11 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G47" s="11" t="inlineStr"/>
+      <c r="G47" s="11" t="inlineStr">
+        <is>
+          <t>[직접 타는 방식] 분유쉐이커와 짝. 분유제조기를 쓸 거면 필요 없습니다</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -2164,7 +2168,7 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>젖병 건조대</t>
+          <t>분유쉐이커</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -2182,7 +2186,11 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G48" s="7" t="inlineStr"/>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>[직접 타는 방식] 분유포트와 짝. 분유제조기를 쓸 거면 필요 없습니다</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
@@ -2197,27 +2205,27 @@
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>분유</t>
+          <t>분유제조기</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>1~2</t>
-        </is>
-      </c>
-      <c r="E49" s="10" t="inlineStr">
-        <is>
-          <t>필수</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>36주</t>
+          <t>34주</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
-          <t>조리원에서 먹던 걸로 준비해두고, 이후 필요에 따라 바꾸세요</t>
+          <t>[자동 방식] 이거 하나면 분유포트·쉐이커가 필요 없습니다. 다만 세척이 번거로워 결국 안 쓰게 됐다는 후기도 많아요</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2242,7 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>분유포트 (보온)</t>
+          <t>보틀워머</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -2252,11 +2260,7 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G50" s="7" t="inlineStr">
-        <is>
-          <t>[직접 타는 방식] 분유쉐이커와 짝. 분유제조기를 쓸 거면 필요 없습니다</t>
-        </is>
-      </c>
+      <c r="G50" s="7" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
@@ -2271,7 +2275,7 @@
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>분유쉐이커</t>
+          <t>분유케이스</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
@@ -2286,12 +2290,12 @@
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>34주</t>
+          <t>36주</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>[직접 타는 방식] 분유포트와 짝. 분유제조기를 쓸 거면 필요 없습니다</t>
+          <t>외출 시</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2312,7 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>분유제조기</t>
+          <t>수유쿠션</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -2328,7 +2332,7 @@
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>[자동 방식] 이거 하나면 분유포트·쉐이커가 필요 없습니다. 다만 세척이 번거로워 결국 안 쓰게 됐다는 후기도 많아요</t>
+          <t>모유수유할 때만 필요합니다</t>
         </is>
       </c>
     </row>
@@ -2345,7 +2349,7 @@
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>보틀워머</t>
+          <t>수유등</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
@@ -2363,7 +2367,11 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G53" s="11" t="inlineStr"/>
+      <c r="G53" s="11" t="inlineStr">
+        <is>
+          <t>새벽에 큰 불 켜면 아기가 깹니다</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -2378,12 +2386,12 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>분유케이스</t>
+          <t>공갈 젖꼭지</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2~3</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -2398,7 +2406,7 @@
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>외출 시</t>
+          <t>안 무는 아기도 있어서 1개 먼저 써보고 늘리세요</t>
         </is>
       </c>
     </row>
@@ -2415,12 +2423,12 @@
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>수유쿠션</t>
+          <t>공갈 젖꼭지 집게 · 케이스</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1세트</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
@@ -2430,12 +2438,12 @@
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>34주</t>
+          <t>36주</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
         <is>
-          <t>모유수유할 때만 필요합니다</t>
+          <t>외출 시 떨어뜨림 방지</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2460,7 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>수유등</t>
+          <t>젖병 집게</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -2472,7 +2480,7 @@
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>새벽에 큰 불 켜면 아기가 깹니다</t>
+          <t>소독 후 뜨거운 젖병 꺼낼 때</t>
         </is>
       </c>
     </row>
@@ -2489,12 +2497,12 @@
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>공갈 젖꼭지</t>
+          <t>젖병 보관함</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>2~3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
@@ -2504,12 +2512,12 @@
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>36주</t>
+          <t>34주</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
         <is>
-          <t>안 무는 아기도 있어서 1개 먼저 써보고 늘리세요</t>
+          <t>먼지 차단</t>
         </is>
       </c>
     </row>
@@ -2526,12 +2534,12 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>공갈 젖꼭지 집게 · 케이스</t>
+          <t>모유 저장팩</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1세트</t>
+          <t>1팩</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -2546,7 +2554,7 @@
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>외출 시 떨어뜨림 방지</t>
+          <t>모유수유·유축하는 경우</t>
         </is>
       </c>
     </row>
@@ -2563,7 +2571,7 @@
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>젖병 집게</t>
+          <t>수유 시트</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
@@ -2578,14 +2586,10 @@
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>34주</t>
-        </is>
-      </c>
-      <c r="G59" s="11" t="inlineStr">
-        <is>
-          <t>소독 후 뜨거운 젖병 꺼낼 때</t>
-        </is>
-      </c>
+          <t>36주</t>
+        </is>
+      </c>
+      <c r="G59" s="11" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -2600,7 +2604,7 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>젖병 보관함</t>
+          <t>트림쿠션</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -2608,21 +2612,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>보통</t>
+      <c r="E60" s="12" t="inlineStr">
+        <is>
+          <t>굳이</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>34주</t>
-        </is>
-      </c>
-      <c r="G60" s="7" t="inlineStr">
-        <is>
-          <t>먼지 차단</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
@@ -2637,27 +2637,27 @@
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>모유 저장팩</t>
+          <t>수유 의자</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>1팩</t>
-        </is>
-      </c>
-      <c r="E61" s="8" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E61" s="12" t="inlineStr">
+        <is>
+          <t>굳이</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>36주</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
         <is>
-          <t>모유수유·유축하는 경우</t>
+          <t>소파나 침대로 충분합니다</t>
         </is>
       </c>
     </row>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>수유 시트</t>
+          <t>분유 디스펜서</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -2682,17 +2682,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>보통</t>
+      <c r="E62" s="12" t="inlineStr">
+        <is>
+          <t>굳이</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>36주</t>
-        </is>
-      </c>
-      <c r="G62" s="7" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>외출이 잦아지면 그때 사도 됩니다</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
@@ -2702,12 +2706,12 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>집 · 수유</t>
+          <t>집 · 수면</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>트림쿠션</t>
+          <t>아기침대 or 범퍼침대</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
@@ -2715,17 +2719,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E63" s="12" t="inlineStr">
-        <is>
-          <t>굳이</t>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G63" s="11" t="inlineStr"/>
+          <t>32주</t>
+        </is>
+      </c>
+      <c r="G63" s="11" t="inlineStr">
+        <is>
+          <t>6개월~1년이면 졸업</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -2735,32 +2743,32 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>집 · 수유</t>
+          <t>집 · 수면</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>수유 의자</t>
+          <t>매트리스 · 방수요</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E64" s="12" t="inlineStr">
-        <is>
-          <t>굳이</t>
+          <t>1~2</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>32주</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>소파나 침대로 충분합니다</t>
+          <t>방수요는 2장 이상 (밤에 갈아야 함)</t>
         </is>
       </c>
     </row>
@@ -2772,34 +2780,30 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>집 · 수유</t>
+          <t>집 · 수면</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>분유 디스펜서</t>
+          <t>침구세트</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E65" s="12" t="inlineStr">
-        <is>
-          <t>굳이</t>
+          <t>1~2</t>
+        </is>
+      </c>
+      <c r="E65" s="10" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G65" s="11" t="inlineStr">
-        <is>
-          <t>외출이 잦아지면 그때 사도 됩니다</t>
-        </is>
-      </c>
+          <t>32주</t>
+        </is>
+      </c>
+      <c r="G65" s="11" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -2814,27 +2818,27 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>아기침대 or 범퍼침대</t>
+          <t>속싸개</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>3~4</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>32주</t>
+          <t>34주</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>6개월~1년이면 졸업</t>
+          <t>생각보다 자주 갈아야 합니다</t>
         </is>
       </c>
     </row>
@@ -2851,27 +2855,27 @@
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>매트리스 · 방수요</t>
+          <t>스와들업</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>1~2</t>
-        </is>
-      </c>
-      <c r="E67" s="10" t="inlineStr">
-        <is>
-          <t>필수</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>32주</t>
+          <t>34주</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr">
         <is>
-          <t>방수요는 2장 이상 (밤에 갈아야 함)</t>
+          <t>모로반사 심한 아기에게</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2892,12 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>침구세트</t>
+          <t>백색소음기</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>1~2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -2903,7 +2907,7 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>32주</t>
+          <t>34주</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr"/>
@@ -2921,27 +2925,27 @@
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>속싸개</t>
+          <t>아기 이불</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>3~4</t>
-        </is>
-      </c>
-      <c r="E69" s="10" t="inlineStr">
-        <is>
-          <t>필수</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>34주</t>
+          <t>32주</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
         <is>
-          <t>생각보다 자주 갈아야 합니다</t>
+          <t>질식 위험이 있어 이불 사용은 권장하지 않습니다. 이불보다 집 온도를 맞춰주세요</t>
         </is>
       </c>
     </row>
@@ -2958,12 +2962,12 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>스와들업</t>
+          <t>암막 커튼</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
@@ -2973,12 +2977,12 @@
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>34주</t>
+          <t>32주</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>모로반사 심한 아기에게</t>
+          <t>낮잠 재울 때 차이가 큽니다</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2999,7 @@
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>백색소음기</t>
+          <t>모로반사 방지 (토닥슈트 등)</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
@@ -3003,9 +3007,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E71" s="10" t="inlineStr">
-        <is>
-          <t>필수</t>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F71" s="8" t="inlineStr">
@@ -3013,7 +3017,11 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G71" s="11" t="inlineStr"/>
+      <c r="G71" s="11" t="inlineStr">
+        <is>
+          <t>속싸개·스와들업으로 안 되면</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -3028,12 +3036,12 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>아기 이불</t>
+          <t>침대 맞춤 패드</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1~2</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
@@ -3046,11 +3054,7 @@
           <t>32주</t>
         </is>
       </c>
-      <c r="G72" s="7" t="inlineStr">
-        <is>
-          <t>질식 위험이 있어 이불 사용은 권장하지 않습니다. 이불보다 집 온도를 맞춰주세요</t>
-        </is>
-      </c>
+      <c r="G72" s="7" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
@@ -3065,12 +3069,12 @@
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>암막 커튼</t>
+          <t>거즈 블랭킷</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
@@ -3080,12 +3084,12 @@
       </c>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>32주</t>
+          <t>34주</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
         <is>
-          <t>낮잠 재울 때 차이가 큽니다</t>
+          <t>덮개 겸 햇빛 가리개</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3106,7 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>모로반사 방지 (토닥슈트 등)</t>
+          <t>타이니 모빌</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -3110,9 +3114,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>보통</t>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -3122,7 +3126,7 @@
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>속싸개·스와들업으로 안 되면</t>
+          <t>부동의 국민 육아템. 커피 한잔의 여유를 느끼세요</t>
         </is>
       </c>
     </row>
@@ -3139,25 +3143,29 @@
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>침대 맞춤 패드</t>
+          <t>태열베개 · 짱구베개</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>1~2</t>
-        </is>
-      </c>
-      <c r="E75" s="8" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="inlineStr">
+        <is>
+          <t>굳이</t>
         </is>
       </c>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>32주</t>
-        </is>
-      </c>
-      <c r="G75" s="11" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G75" s="11" t="inlineStr">
+        <is>
+          <t>뒤집기 시작하면 안전 문제로 못 씁니다 (4~6개월)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -3172,27 +3180,27 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>거즈 블랭킷</t>
+          <t>바디필로우</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E76" s="12" t="inlineStr">
+        <is>
+          <t>굳이</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>34주</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>덮개 겸 햇빛 가리개</t>
+          <t>역방쿠·수유시트가 있으면 잘 안 씁니다</t>
         </is>
       </c>
     </row>
@@ -3204,12 +3212,12 @@
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>집 · 수면</t>
+          <t>집 · 목욕/위생</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>모빌</t>
+          <t>아기 욕조</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
@@ -3217,21 +3225,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E77" s="12" t="inlineStr">
-        <is>
-          <t>굳이</t>
+      <c r="E77" s="10" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G77" s="11" t="inlineStr">
-        <is>
-          <t>흥미를 금방 잃습니다</t>
-        </is>
-      </c>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G77" s="11" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -3241,32 +3245,32 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>집 · 수면</t>
+          <t>집 · 목욕/위생</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>태열베개 · 짱구베개</t>
+          <t>가제 손수건</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E78" s="12" t="inlineStr">
-        <is>
-          <t>굳이</t>
+          <t>20~30</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>34주</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>뒤집기 시작하면 안전 문제로 못 씁니다 (4~6개월)</t>
+          <t>아주 부드러워서 얼굴·입 안처럼 자극이 적어야 하는 곳에 씁니다. 제일 많이 쓰는 물건이에요</t>
         </is>
       </c>
     </row>
@@ -3278,32 +3282,32 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>집 · 수면</t>
+          <t>집 · 목욕/위생</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>바디필로우</t>
+          <t>엠보 손수건</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E79" s="12" t="inlineStr">
-        <is>
-          <t>굳이</t>
+          <t>10~20</t>
+        </is>
+      </c>
+      <c r="E79" s="10" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>34주</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr">
         <is>
-          <t>역방쿠·수유시트가 있으면 잘 안 씁니다</t>
+          <t>가제보다 아주 조금 거칩니다. 엉덩이·팔 등 얼굴 외에 씁니다</t>
         </is>
       </c>
     </row>
@@ -3320,12 +3324,12 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>아기 욕조</t>
+          <t>샤워 타월 (또는 천기저귀)</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -3338,7 +3342,11 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G80" s="7" t="inlineStr"/>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>목욕 후에 씁니다</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
@@ -3353,12 +3361,12 @@
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>가제 손수건</t>
+          <t>아기 워시 · 샴푸</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>20~30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E81" s="10" t="inlineStr">
@@ -3371,11 +3379,7 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G81" s="11" t="inlineStr">
-        <is>
-          <t>아주 부드러워서 얼굴·입 안처럼 자극이 적어야 하는 곳에 씁니다. 제일 많이 쓰는 물건이에요</t>
-        </is>
-      </c>
+      <c r="G81" s="11" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -3390,12 +3394,12 @@
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>엠보 손수건</t>
+          <t>로션 · 크림</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>10~20</t>
+          <t>1~2</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -3408,11 +3412,7 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G82" s="7" t="inlineStr">
-        <is>
-          <t>가제보다 아주 조금 거칩니다. 엉덩이·팔 등 얼굴 외에 씁니다</t>
-        </is>
-      </c>
+      <c r="G82" s="7" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>샤워 타월 (또는 천기저귀)</t>
+          <t>기저귀 크림 (연고)</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E83" s="10" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="G83" s="11" t="inlineStr">
         <is>
-          <t>목욕 후에 씁니다</t>
+          <t>기저귀 발진 시 (판테놀)</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>아기 워시 · 샴푸</t>
+          <t>아기 오일</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -3472,9 +3472,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E84" s="6" t="inlineStr">
-        <is>
-          <t>필수</t>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -3482,7 +3482,11 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G84" s="7" t="inlineStr"/>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>태열·각질 관리</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="8" t="inlineStr">
@@ -3497,17 +3501,17 @@
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>로션 · 크림</t>
+          <t>탕온도계</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>1~2</t>
-        </is>
-      </c>
-      <c r="E85" s="10" t="inlineStr">
-        <is>
-          <t>필수</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F85" s="8" t="inlineStr">
@@ -3515,7 +3519,11 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G85" s="11" t="inlineStr"/>
+      <c r="G85" s="11" t="inlineStr">
+        <is>
+          <t>목욕물 37~38도. 손 감각은 생각보다 부정확합니다</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -3530,7 +3538,7 @@
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>기저귀 크림</t>
+          <t>샴푸 헤어캡</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -3538,9 +3546,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E86" s="6" t="inlineStr">
-        <is>
-          <t>필수</t>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -3550,7 +3558,7 @@
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>기저귀 발진은 거의 반드시 옵니다</t>
+          <t>눈에 물 안 들어가게</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3575,12 @@
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>판테놀 연고</t>
+          <t>소독 티슈 · 제균 스프레이</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1세트</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -3587,7 +3595,7 @@
       </c>
       <c r="G87" s="11" t="inlineStr">
         <is>
-          <t>발진·트러블 났을 때. 약국에서 삽니다</t>
+          <t>장난감·바닥용</t>
         </is>
       </c>
     </row>
@@ -3604,12 +3612,12 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>아기 오일</t>
+          <t>지퍼백</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1팩</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
@@ -3624,7 +3632,7 @@
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>태열·각질 관리</t>
+          <t>외출용 소분</t>
         </is>
       </c>
     </row>
@@ -3641,17 +3649,17 @@
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>탕온도계</t>
+          <t>아기 손톱가위 · 면봉</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E89" s="8" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>1세트</t>
+        </is>
+      </c>
+      <c r="E89" s="10" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F89" s="8" t="inlineStr">
@@ -3659,11 +3667,7 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G89" s="11" t="inlineStr">
-        <is>
-          <t>목욕물 37~38도. 손 감각은 생각보다 부정확합니다</t>
-        </is>
-      </c>
+      <c r="G89" s="11" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -3678,7 +3682,7 @@
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>샴푸 헤어캡</t>
+          <t>체온계</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -3686,9 +3690,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>보통</t>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
@@ -3696,11 +3700,7 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G90" s="7" t="inlineStr">
-        <is>
-          <t>눈에 물 안 들어가게</t>
-        </is>
-      </c>
+      <c r="G90" s="7" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>소독 티슈 · 제균 스프레이</t>
+          <t>배꼽소독 용품</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
@@ -3723,9 +3723,9 @@
           <t>1세트</t>
         </is>
       </c>
-      <c r="E91" s="8" t="inlineStr">
-        <is>
-          <t>보통</t>
+      <c r="E91" s="10" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F91" s="8" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="G91" s="11" t="inlineStr">
         <is>
-          <t>장난감·바닥용</t>
+          <t>퇴원 직후 바로 씁니다</t>
         </is>
       </c>
     </row>
@@ -3752,27 +3752,27 @@
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>지퍼백</t>
+          <t>기저귀 (신생아용)</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>1팩</t>
-        </is>
-      </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>1~2팩</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>34주</t>
+          <t>36주</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>물티슈 덜어 담기, 외출용 소분</t>
+          <t>사이즈가 금방 바뀝니다. 대량 구매 금물</t>
         </is>
       </c>
     </row>
@@ -3789,12 +3789,12 @@
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>아기 손톱가위 · 면봉</t>
+          <t>물티슈</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>1세트</t>
+          <t>대량</t>
         </is>
       </c>
       <c r="E93" s="10" t="inlineStr">
@@ -3807,7 +3807,11 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G93" s="11" t="inlineStr"/>
+      <c r="G93" s="11" t="inlineStr">
+        <is>
+          <t>이건 많이 사도 됩니다</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -3822,7 +3826,7 @@
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>체온계</t>
+          <t>기저귀 휴지통</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -3830,9 +3834,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E94" s="6" t="inlineStr">
-        <is>
-          <t>필수</t>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
@@ -3840,7 +3844,11 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G94" s="7" t="inlineStr"/>
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>밀폐력만 좋으면 충분합니다</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
@@ -3855,12 +3863,12 @@
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>배꼽소독 용품</t>
+          <t>아기 비데</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>1세트</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E95" s="10" t="inlineStr">
@@ -3875,7 +3883,7 @@
       </c>
       <c r="G95" s="11" t="inlineStr">
         <is>
-          <t>퇴원 직후 바로 씁니다</t>
+          <t>엄마 손목 지킴이입니다</t>
         </is>
       </c>
     </row>
@@ -3892,27 +3900,27 @@
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>기저귀 (신생아용)</t>
+          <t>콧물흡입기 (노시부)</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>1~2팩</t>
-        </is>
-      </c>
-      <c r="E96" s="6" t="inlineStr">
-        <is>
-          <t>필수</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E96" s="12" t="inlineStr">
+        <is>
+          <t>굳이</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>36주</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>사이즈가 금방 바뀝니다. 대량 구매 금물</t>
+          <t>신생아 때는 거의 안 씁니다. 아플 때 사도 늦지 않아요</t>
         </is>
       </c>
     </row>
@@ -3929,17 +3937,17 @@
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>물티슈</t>
+          <t>기저귀 갈이대</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>대량</t>
-        </is>
-      </c>
-      <c r="E97" s="10" t="inlineStr">
-        <is>
-          <t>필수</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F97" s="8" t="inlineStr">
@@ -3949,7 +3957,7 @@
       </c>
       <c r="G97" s="11" t="inlineStr">
         <is>
-          <t>이건 많이 사도 됩니다</t>
+          <t>허리 보호에 도움이 됩니다</t>
         </is>
       </c>
     </row>
@@ -3961,22 +3969,22 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>집 · 목욕/위생</t>
+          <t>집 · 의류</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>기저귀 휴지통</t>
+          <t>배냇저고리</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
@@ -3984,11 +3992,7 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G98" s="7" t="inlineStr">
-        <is>
-          <t>밀폐력만 좋으면 충분합니다</t>
-        </is>
-      </c>
+      <c r="G98" s="7" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
@@ -3998,17 +4002,17 @@
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>집 · 목욕/위생</t>
+          <t>집 · 의류</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>아기 비데</t>
+          <t>바디슈트 · 우주복</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5~7</t>
         </is>
       </c>
       <c r="E99" s="10" t="inlineStr">
@@ -4023,7 +4027,7 @@
       </c>
       <c r="G99" s="11" t="inlineStr">
         <is>
-          <t>엄마 손목 지킴이입니다</t>
+          <t>신생아 사이즈는 한 달이면 끝납니다</t>
         </is>
       </c>
     </row>
@@ -4035,34 +4039,30 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>집 · 목욕/위생</t>
+          <t>집 · 의류</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>콧물흡입기 (노시부)</t>
+          <t>손싸개 · 발싸개</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E100" s="12" t="inlineStr">
-        <is>
-          <t>굳이</t>
+          <t>2~3</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G100" s="7" t="inlineStr">
-        <is>
-          <t>신생아 때는 거의 안 씁니다. 아플 때 사도 늦지 않아요</t>
-        </is>
-      </c>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G100" s="7" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
@@ -4072,34 +4072,30 @@
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>집 · 목욕/위생</t>
+          <t>집 · 의류</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>기저귀 갈이대</t>
+          <t>턱받이</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E101" s="12" t="inlineStr">
-        <is>
-          <t>굳이</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F101" s="8" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G101" s="11" t="inlineStr">
-        <is>
-          <t>바닥이나 침대에서 갈게 됩니다</t>
-        </is>
-      </c>
+          <t>출산 후</t>
+        </is>
+      </c>
+      <c r="G101" s="11" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -4114,17 +4110,17 @@
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>배냇저고리</t>
+          <t>신생아 양말</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E102" s="6" t="inlineStr">
-        <is>
-          <t>필수</t>
+          <t>3~5</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
@@ -4147,17 +4143,17 @@
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>바디슈트 · 우주복</t>
+          <t>배냇수트 (반팔·긴팔)</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>5~7</t>
-        </is>
-      </c>
-      <c r="E103" s="10" t="inlineStr">
-        <is>
-          <t>필수</t>
+          <t>2~3</t>
+        </is>
+      </c>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F103" s="8" t="inlineStr">
@@ -4167,7 +4163,7 @@
       </c>
       <c r="G103" s="11" t="inlineStr">
         <is>
-          <t>신생아 사이즈는 한 달이면 끝납니다</t>
+          <t>배냇저고리 다음 단계</t>
         </is>
       </c>
     </row>
@@ -4184,7 +4180,7 @@
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>손싸개 · 발싸개</t>
+          <t>내복</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -4199,10 +4195,14 @@
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>34주</t>
-        </is>
-      </c>
-      <c r="G104" s="7" t="inlineStr"/>
+          <t>출산 후</t>
+        </is>
+      </c>
+      <c r="G104" s="7" t="inlineStr">
+        <is>
+          <t>우주복 안에 입힙니다</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
@@ -4217,22 +4217,22 @@
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>턱받이</t>
+          <t>아기 전용 세제</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E105" s="8" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E105" s="10" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F105" s="8" t="inlineStr">
         <is>
-          <t>출산 후</t>
+          <t>34주</t>
         </is>
       </c>
       <c r="G105" s="11" t="inlineStr"/>
@@ -4250,12 +4250,12 @@
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>신생아 양말</t>
+          <t>무형광 세탁망</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>3~5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
@@ -4268,7 +4268,11 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G106" s="7" t="inlineStr"/>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>아기 옷은 따로 세탁합니다</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
@@ -4283,12 +4287,12 @@
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>배냇수트 (반팔·긴팔)</t>
+          <t>아기 옷걸이</t>
         </is>
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>2~3</t>
+          <t>1세트</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -4303,7 +4307,7 @@
       </c>
       <c r="G107" s="11" t="inlineStr">
         <is>
-          <t>배냇저고리 다음 단계</t>
+          <t>어른 옷걸이엔 안 걸립니다</t>
         </is>
       </c>
     </row>
@@ -4320,27 +4324,27 @@
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>내복</t>
+          <t>신생아 신발</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>2~3</t>
-        </is>
-      </c>
-      <c r="E108" s="4" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E108" s="12" t="inlineStr">
+        <is>
+          <t>굳이</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>출산 후</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
-          <t>우주복 안에 입힙니다</t>
+          <t>걷기 전엔 사진용입니다</t>
         </is>
       </c>
     </row>
@@ -4352,12 +4356,12 @@
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>집 · 의류</t>
+          <t>집 · 외출</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>아기 전용 세제</t>
+          <t>카시트</t>
         </is>
       </c>
       <c r="D109" s="8" t="inlineStr">
@@ -4372,10 +4376,14 @@
       </c>
       <c r="F109" s="8" t="inlineStr">
         <is>
-          <t>34주</t>
-        </is>
-      </c>
-      <c r="G109" s="11" t="inlineStr"/>
+          <t>32주</t>
+        </is>
+      </c>
+      <c r="G109" s="11" t="inlineStr">
+        <is>
+          <t>중고 금지 — 사고 이력 확인 불가</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
@@ -4385,32 +4393,32 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>집 · 의류</t>
+          <t>집 · 외출</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>무형광 세탁망</t>
+          <t>유모차</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>34주</t>
+          <t>32주</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
-          <t>아기 옷은 따로 세탁합니다</t>
+          <t>디럭스/절충형 미리 비교해두세요</t>
         </is>
       </c>
     </row>
@@ -4422,22 +4430,22 @@
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>집 · 의류</t>
+          <t>집 · 외출</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>아기 옷걸이</t>
+          <t>아기띠</t>
         </is>
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>1세트</t>
-        </is>
-      </c>
-      <c r="E111" s="8" t="inlineStr">
-        <is>
-          <t>보통</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E111" s="10" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F111" s="8" t="inlineStr">
@@ -4447,7 +4455,7 @@
       </c>
       <c r="G111" s="11" t="inlineStr">
         <is>
-          <t>어른 옷걸이엔 안 걸립니다</t>
+          <t>신생아용 인서트 확인</t>
         </is>
       </c>
     </row>
@@ -4459,32 +4467,32 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>집 · 의류</t>
+          <t>집 · 외출</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>신생아 신발</t>
+          <t>카시트 후방거울</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E112" s="12" t="inlineStr">
-        <is>
-          <t>굳이</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>34주</t>
         </is>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
-          <t>걷기 전엔 사진용입니다</t>
+          <t>운전 중 아기 상태 확인</t>
         </is>
       </c>
     </row>
@@ -4501,27 +4509,27 @@
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>카시트</t>
+          <t>유모차 가리개 · 라이너</t>
         </is>
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E113" s="10" t="inlineStr">
-        <is>
-          <t>필수</t>
+          <t>1세트</t>
+        </is>
+      </c>
+      <c r="E113" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F113" s="8" t="inlineStr">
         <is>
-          <t>32주</t>
+          <t>36주</t>
         </is>
       </c>
       <c r="G113" s="11" t="inlineStr">
         <is>
-          <t>중고 금지 — 사고 이력 확인 불가</t>
+          <t>햇빛·계절 대응</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4546,7 @@
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>유모차</t>
+          <t>기저귀 가방</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
@@ -4546,19 +4554,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E114" s="6" t="inlineStr">
-        <is>
-          <t>필수</t>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>32주</t>
+          <t>36주</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>디럭스/절충형 미리 비교해두세요</t>
+          <t>에코백으로 대체 가능</t>
         </is>
       </c>
     </row>
@@ -4575,7 +4583,7 @@
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>아기띠</t>
+          <t>휴대용 기저귀 매트</t>
         </is>
       </c>
       <c r="D115" s="8" t="inlineStr">
@@ -4583,21 +4591,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E115" s="10" t="inlineStr">
-        <is>
-          <t>필수</t>
+      <c r="E115" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F115" s="8" t="inlineStr">
         <is>
-          <t>34주</t>
-        </is>
-      </c>
-      <c r="G115" s="11" t="inlineStr">
-        <is>
-          <t>신생아용 인서트 확인</t>
-        </is>
-      </c>
+          <t>36주</t>
+        </is>
+      </c>
+      <c r="G115" s="11" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
@@ -4612,7 +4616,7 @@
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>카시트 후방거울</t>
+          <t>유모차 방한 · 방수커버</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
@@ -4627,12 +4631,12 @@
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>34주</t>
+          <t>계절 맞춰</t>
         </is>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>운전 중 아기 상태 확인</t>
+          <t>겨울 출산이면 미리 준비</t>
         </is>
       </c>
     </row>
@@ -4644,17 +4648,17 @@
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>집 · 외출</t>
+          <t>집 · 기타</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>유모차 가리개 · 라이너</t>
+          <t>가습기</t>
         </is>
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>1세트</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -4664,12 +4668,12 @@
       </c>
       <c r="F117" s="8" t="inlineStr">
         <is>
-          <t>36주</t>
+          <t>34주</t>
         </is>
       </c>
       <c r="G117" s="11" t="inlineStr">
         <is>
-          <t>햇빛·계절 대응</t>
+          <t>겨울 출산이면 필수에 가깝습니다</t>
         </is>
       </c>
     </row>
@@ -4681,12 +4685,12 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>집 · 외출</t>
+          <t>집 · 기타</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>기저귀 가방</t>
+          <t>공기청정기</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
@@ -4701,14 +4705,10 @@
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>36주</t>
-        </is>
-      </c>
-      <c r="G118" s="7" t="inlineStr">
-        <is>
-          <t>에코백으로 대체 가능</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G118" s="7" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
@@ -4718,12 +4718,12 @@
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>집 · 외출</t>
+          <t>집 · 기타</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>휴대용 기저귀 매트</t>
+          <t>온습도계</t>
         </is>
       </c>
       <c r="D119" s="8" t="inlineStr">
@@ -4738,10 +4738,14 @@
       </c>
       <c r="F119" s="8" t="inlineStr">
         <is>
-          <t>36주</t>
-        </is>
-      </c>
-      <c r="G119" s="11" t="inlineStr"/>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G119" s="11" t="inlineStr">
+        <is>
+          <t>아기방 온도 22~24도 / 습도 50~60%</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
@@ -4751,17 +4755,17 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>집 · 외출</t>
+          <t>집 · 기타</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>유모차 방한 · 방수커버</t>
+          <t>수유일지 (앱/노트)</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
@@ -4771,12 +4775,12 @@
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>계절 맞춰</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
-          <t>겨울 출산이면 미리 준비</t>
+          <t>수유텀·배변 기록. 병원 갈 때 도움됨</t>
         </is>
       </c>
     </row>
@@ -4793,7 +4797,7 @@
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>가습기</t>
+          <t>산모 영양제 (철분·유산균)</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
@@ -4801,21 +4805,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E121" s="8" t="inlineStr">
-        <is>
-          <t>보통</t>
+      <c r="E121" s="10" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F121" s="8" t="inlineStr">
         <is>
-          <t>34주</t>
-        </is>
-      </c>
-      <c r="G121" s="11" t="inlineStr">
-        <is>
-          <t>겨울 출산이면 필수에 가깝습니다</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G121" s="11" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>공기청정기</t>
+          <t>아기체육관 · 플레이매트</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
@@ -4845,10 +4845,14 @@
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G122" s="7" t="inlineStr"/>
+          <t>출산 후</t>
+        </is>
+      </c>
+      <c r="G122" s="7" t="inlineStr">
+        <is>
+          <t>3개월 이후에 사도 됩니다</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="8" t="inlineStr">
@@ -4863,7 +4867,7 @@
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>온습도계</t>
+          <t>바운서</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr">
@@ -4871,19 +4875,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E123" s="8" t="inlineStr">
-        <is>
-          <t>보통</t>
+      <c r="E123" s="12" t="inlineStr">
+        <is>
+          <t>굳이</t>
         </is>
       </c>
       <c r="F123" s="8" t="inlineStr">
         <is>
-          <t>34주</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G123" s="11" t="inlineStr">
         <is>
-          <t>아기방 온도 22~24도 / 습도 50~60%</t>
+          <t>안 타는 아기가 많습니다. 중고로 먼저 시도</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4904,7 @@
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>손소독제</t>
+          <t>역류방지쿠션</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
@@ -4908,21 +4912,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>보통</t>
+      <c r="E124" s="12" t="inlineStr">
+        <is>
+          <t>굳이</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>34주</t>
-        </is>
-      </c>
-      <c r="G124" s="7" t="inlineStr">
-        <is>
-          <t>방문객용</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G124" s="7" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="8" t="inlineStr">
@@ -4937,27 +4937,27 @@
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>수유일지 (앱/노트)</t>
+          <t>아기 체중계</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E125" s="12" t="inlineStr">
+        <is>
+          <t>굳이</t>
+        </is>
+      </c>
+      <c r="F125" s="8" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E125" s="8" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="F125" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="G125" s="11" t="inlineStr">
         <is>
-          <t>수유텀·배변 기록. 병원 갈 때 도움됨</t>
+          <t>병원·보건소에서 잽니다</t>
         </is>
       </c>
     </row>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>산모 영양제 (철분·유산균)</t>
+          <t>열탕소독기</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
@@ -4982,9 +4982,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E126" s="6" t="inlineStr">
-        <is>
-          <t>필수</t>
+      <c r="E126" s="12" t="inlineStr">
+        <is>
+          <t>굳이</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
@@ -4992,7 +4992,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G126" s="7" t="inlineStr"/>
+      <c r="G126" s="7" t="inlineStr">
+        <is>
+          <t>냄비로 충분합니다</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
@@ -5007,7 +5011,7 @@
       </c>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t>아기체육관 · 플레이매트</t>
+          <t>젖병 건조 트레이</t>
         </is>
       </c>
       <c r="D127" s="8" t="inlineStr">
@@ -5022,14 +5026,10 @@
       </c>
       <c r="F127" s="8" t="inlineStr">
         <is>
-          <t>출산 후</t>
-        </is>
-      </c>
-      <c r="G127" s="11" t="inlineStr">
-        <is>
-          <t>3개월 이후에 사도 됩니다</t>
-        </is>
-      </c>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G127" s="11" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
@@ -5044,29 +5044,25 @@
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>바운서</t>
+          <t>방수요 (여분)</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E128" s="12" t="inlineStr">
-        <is>
-          <t>굳이</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E128" s="6" t="inlineStr">
+        <is>
+          <t>필수</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G128" s="7" t="inlineStr">
-        <is>
-          <t>안 타는 아기가 많습니다. 중고로 먼저 시도</t>
-        </is>
-      </c>
+          <t>34주</t>
+        </is>
+      </c>
+      <c r="G128" s="7" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
@@ -5081,25 +5077,29 @@
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>역류방지쿠션</t>
+          <t>유축기 개인부품</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E129" s="12" t="inlineStr">
-        <is>
-          <t>굳이</t>
+          <t>1세트</t>
+        </is>
+      </c>
+      <c r="E129" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F129" s="8" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G129" s="11" t="inlineStr"/>
+          <t>36주</t>
+        </is>
+      </c>
+      <c r="G129" s="11" t="inlineStr">
+        <is>
+          <t>대여 시 부품만 새로 구매</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>아기 체중계</t>
+          <t>아기 손톱 줄 (파일)</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
@@ -5122,19 +5122,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E130" s="12" t="inlineStr">
-        <is>
-          <t>굳이</t>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>34주</t>
         </is>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
-          <t>병원·보건소에서 잽니다</t>
+          <t>가위가 무서우면 이걸로</t>
         </is>
       </c>
     </row>
@@ -5151,17 +5151,17 @@
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>열탕소독기</t>
+          <t>수유 시간 알람 (앱)</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E131" s="12" t="inlineStr">
-        <is>
-          <t>굳이</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E131" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F131" s="8" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="G131" s="11" t="inlineStr">
         <is>
-          <t>냄비로 충분합니다</t>
+          <t>2~3시간 간격, 처음엔 놓치기 쉽습니다</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>젖병 건조 트레이</t>
+          <t>제습기</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
@@ -5203,10 +5203,14 @@
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>34주</t>
-        </is>
-      </c>
-      <c r="G132" s="7" t="inlineStr"/>
+          <t>계절 맞춰</t>
+        </is>
+      </c>
+      <c r="G132" s="7" t="inlineStr">
+        <is>
+          <t>여름 출산이면</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="8" t="inlineStr">
@@ -5221,17 +5225,17 @@
       </c>
       <c r="C133" s="9" t="inlineStr">
         <is>
-          <t>방수요 (여분)</t>
+          <t>대형 빨래 건조대</t>
         </is>
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E133" s="10" t="inlineStr">
-        <is>
-          <t>필수</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E133" s="8" t="inlineStr">
+        <is>
+          <t>보통</t>
         </is>
       </c>
       <c r="F133" s="8" t="inlineStr">
@@ -5239,7 +5243,11 @@
           <t>34주</t>
         </is>
       </c>
-      <c r="G133" s="11" t="inlineStr"/>
+      <c r="G133" s="11" t="inlineStr">
+        <is>
+          <t>아기 빨래가 매일 나옵니다</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
@@ -5254,12 +5262,12 @@
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>유축기 개인부품</t>
+          <t>아기 수납장 · 서랍장</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>1세트</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
@@ -5269,12 +5277,12 @@
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>36주</t>
+          <t>32주</t>
         </is>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
-          <t>대여 시 부품만 새로 구매</t>
+          <t>기저귀·옷 정리용</t>
         </is>
       </c>
     </row>
@@ -5291,7 +5299,7 @@
       </c>
       <c r="C135" s="9" t="inlineStr">
         <is>
-          <t>아기 손톱 줄 (파일)</t>
+          <t>흑백 초점책</t>
         </is>
       </c>
       <c r="D135" s="8" t="inlineStr">
@@ -5306,12 +5314,12 @@
       </c>
       <c r="F135" s="8" t="inlineStr">
         <is>
-          <t>34주</t>
+          <t>출산 후</t>
         </is>
       </c>
       <c r="G135" s="11" t="inlineStr">
         <is>
-          <t>가위가 무서우면 이걸로</t>
+          <t>신생아 시력 발달용. 3개월 내외까지</t>
         </is>
       </c>
     </row>
@@ -5328,12 +5336,12 @@
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>수유 시간 알람 (앱)</t>
+          <t>거실 매트</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
@@ -5343,12 +5351,12 @@
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>출산 후</t>
         </is>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
-          <t>2~3시간 간격, 처음엔 놓치기 쉽습니다</t>
+          <t>기기 시작할 때. 미리 안 사도 됩니다</t>
         </is>
       </c>
     </row>
@@ -5365,7 +5373,7 @@
       </c>
       <c r="C137" s="9" t="inlineStr">
         <is>
-          <t>제습기</t>
+          <t>범보의자</t>
         </is>
       </c>
       <c r="D137" s="8" t="inlineStr">
@@ -5380,12 +5388,12 @@
       </c>
       <c r="F137" s="8" t="inlineStr">
         <is>
-          <t>계절 맞춰</t>
+          <t>출산 후</t>
         </is>
       </c>
       <c r="G137" s="11" t="inlineStr">
         <is>
-          <t>여름 출산이면</t>
+          <t>앉기 연습용. 3~6개월부터</t>
         </is>
       </c>
     </row>
@@ -5402,7 +5410,7 @@
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>대형 빨래 건조대</t>
+          <t>아기 전용 세탁기</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
@@ -5410,19 +5418,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr">
-        <is>
-          <t>보통</t>
+      <c r="E138" s="12" t="inlineStr">
+        <is>
+          <t>굳이</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>34주</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
-          <t>아기 빨래가 매일 나옵니다</t>
+          <t>일반 세탁기 + 아기 세제로 충분합니다</t>
         </is>
       </c>
     </row>
@@ -5439,7 +5447,7 @@
       </c>
       <c r="C139" s="9" t="inlineStr">
         <is>
-          <t>아기 수납장 · 서랍장</t>
+          <t>아기 수영장 · 목튜브</t>
         </is>
       </c>
       <c r="D139" s="8" t="inlineStr">
@@ -5447,283 +5455,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E139" s="8" t="inlineStr">
-        <is>
-          <t>보통</t>
+      <c r="E139" s="12" t="inlineStr">
+        <is>
+          <t>굳이</t>
         </is>
       </c>
       <c r="F139" s="8" t="inlineStr">
         <is>
-          <t>32주</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G139" s="11" t="inlineStr">
         <is>
-          <t>기저귀·옷 정리용</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B140" s="5" t="inlineStr">
-        <is>
-          <t>집 · 기타</t>
-        </is>
-      </c>
-      <c r="C140" s="5" t="inlineStr">
-        <is>
-          <t>기저귀 트롤리</t>
-        </is>
-      </c>
-      <c r="D140" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E140" s="4" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="inlineStr">
-        <is>
-          <t>34주</t>
-        </is>
-      </c>
-      <c r="G140" s="7" t="inlineStr">
-        <is>
-          <t>갈이대 옆에 두고 씁니다</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B141" s="9" t="inlineStr">
-        <is>
-          <t>집 · 기타</t>
-        </is>
-      </c>
-      <c r="C141" s="9" t="inlineStr">
-        <is>
-          <t>흑백 초점책</t>
-        </is>
-      </c>
-      <c r="D141" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E141" s="8" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="F141" s="8" t="inlineStr">
-        <is>
-          <t>출산 후</t>
-        </is>
-      </c>
-      <c r="G141" s="11" t="inlineStr">
-        <is>
-          <t>신생아 시력 발달용. 3개월 내외까지</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B142" s="5" t="inlineStr">
-        <is>
-          <t>집 · 기타</t>
-        </is>
-      </c>
-      <c r="C142" s="5" t="inlineStr">
-        <is>
-          <t>거실 매트</t>
-        </is>
-      </c>
-      <c r="D142" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E142" s="4" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="F142" s="4" t="inlineStr">
-        <is>
-          <t>출산 후</t>
-        </is>
-      </c>
-      <c r="G142" s="7" t="inlineStr">
-        <is>
-          <t>기기 시작할 때. 미리 안 사도 됩니다</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B143" s="9" t="inlineStr">
-        <is>
-          <t>집 · 기타</t>
-        </is>
-      </c>
-      <c r="C143" s="9" t="inlineStr">
-        <is>
-          <t>범보의자</t>
-        </is>
-      </c>
-      <c r="D143" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E143" s="8" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="F143" s="8" t="inlineStr">
-        <is>
-          <t>출산 후</t>
-        </is>
-      </c>
-      <c r="G143" s="11" t="inlineStr">
-        <is>
-          <t>앉기 연습용. 3~6개월부터</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B144" s="5" t="inlineStr">
-        <is>
-          <t>집 · 기타</t>
-        </is>
-      </c>
-      <c r="C144" s="5" t="inlineStr">
-        <is>
-          <t>초음파 · 주사 앨범</t>
-        </is>
-      </c>
-      <c r="D144" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>보통</t>
-        </is>
-      </c>
-      <c r="F144" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G144" s="7" t="inlineStr">
-        <is>
-          <t>기록용</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="8" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B145" s="9" t="inlineStr">
-        <is>
-          <t>집 · 기타</t>
-        </is>
-      </c>
-      <c r="C145" s="9" t="inlineStr">
-        <is>
-          <t>아기 전용 세탁기</t>
-        </is>
-      </c>
-      <c r="D145" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E145" s="12" t="inlineStr">
-        <is>
-          <t>굳이</t>
-        </is>
-      </c>
-      <c r="F145" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G145" s="11" t="inlineStr">
-        <is>
-          <t>일반 세탁기 + 아기 세제로 충분합니다</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B146" s="5" t="inlineStr">
-        <is>
-          <t>집 · 기타</t>
-        </is>
-      </c>
-      <c r="C146" s="5" t="inlineStr">
-        <is>
-          <t>아기 수영장 · 목튜브</t>
-        </is>
-      </c>
-      <c r="D146" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E146" s="12" t="inlineStr">
-        <is>
-          <t>굳이</t>
-        </is>
-      </c>
-      <c r="F146" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G146" s="7" t="inlineStr">
-        <is>
           <t>100일 전후 잠깐 이벤트용</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G146"/>
+  <autoFilter ref="A3:G139"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
